--- a/companies/alder-ridge/source-files/Shared/Finance/Reporting/2026/06 June/Q2 management reporting data book - v7 controller tie.xlsx
+++ b/companies/alder-ridge/source-files/Shared/Finance/Reporting/2026/06 June/Q2 management reporting data book - v7 controller tie.xlsx
@@ -10,7 +10,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Quarterly KPIs'!$A$4:$M$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Board Performance'!$A$4:$M$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Board Performance'!$A$4:$M$220</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -3316,7 +3316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M206"/>
+  <dimension ref="A1:M220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9175,17 +9175,17 @@
     <row r="106">
       <c r="A106" s="36" t="inlineStr">
         <is>
-          <t>RPT-00232</t>
+          <t>RPT-072X01</t>
         </is>
       </c>
       <c r="B106" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C106" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Approved lender metric basis</t>
         </is>
       </c>
       <c r="D106" s="27" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="E106" s="27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>LTM 2026-06-30</t>
         </is>
       </c>
       <c r="F106" s="27" t="inlineStr">
@@ -9205,16 +9205,16 @@
       </c>
       <c r="G106" s="27" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Adjusted EBITDA</t>
         </is>
       </c>
       <c r="H106" s="44" t="n">
-        <v>0.2</v>
+        <v>6218011.41</v>
       </c>
       <c r="I106" s="27" t="inlineStr"/>
       <c r="J106" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K106" s="27" t="inlineStr">
@@ -9232,17 +9232,17 @@
     <row r="107">
       <c r="A107" s="36" t="inlineStr">
         <is>
-          <t>RPT-00233</t>
+          <t>RPT-072X02</t>
         </is>
       </c>
       <c r="B107" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Approved lender metric basis</t>
         </is>
       </c>
       <c r="D107" s="27" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="E107" s="27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F107" s="27" t="inlineStr">
@@ -9262,16 +9262,16 @@
       </c>
       <c r="G107" s="27" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Funded debt</t>
         </is>
       </c>
       <c r="H107" s="44" t="n">
-        <v>49800000</v>
+        <v>1</v>
       </c>
       <c r="I107" s="27" t="inlineStr"/>
       <c r="J107" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>ledger allocation factor</t>
         </is>
       </c>
       <c r="K107" s="27" t="inlineStr">
@@ -9284,22 +9284,26 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="M107" s="27" t="inlineStr"/>
+      <c r="M107" s="27" t="inlineStr">
+        <is>
+          <t>Vista ERP balance sheet as of 2026-06-30; accounts 2200, 2210, and 2300</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="36" t="inlineStr">
         <is>
-          <t>RPT-00234</t>
+          <t>RPT-072X03</t>
         </is>
       </c>
       <c r="B108" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C108" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Approved lender metric basis</t>
         </is>
       </c>
       <c r="D108" s="27" t="inlineStr">
@@ -9309,7 +9313,7 @@
       </c>
       <c r="E108" s="27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>LTM 2026-06-30</t>
         </is>
       </c>
       <c r="F108" s="27" t="inlineStr">
@@ -9319,16 +9323,16 @@
       </c>
       <c r="G108" s="27" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Cash interest LTM</t>
         </is>
       </c>
       <c r="H108" s="44" t="n">
-        <v>0.26</v>
+        <v>620</v>
       </c>
       <c r="I108" s="27" t="inlineStr"/>
       <c r="J108" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K108" s="27" t="inlineStr">
@@ -9346,17 +9350,17 @@
     <row r="109">
       <c r="A109" s="36" t="inlineStr">
         <is>
-          <t>RPT-00235</t>
+          <t>RPT-072X04</t>
         </is>
       </c>
       <c r="B109" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C109" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Approved lender metric basis</t>
         </is>
       </c>
       <c r="D109" s="27" t="inlineStr">
@@ -9366,7 +9370,7 @@
       </c>
       <c r="E109" s="27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>LTM 2026-06-30</t>
         </is>
       </c>
       <c r="F109" s="27" t="inlineStr">
@@ -9376,16 +9380,16 @@
       </c>
       <c r="G109" s="27" t="inlineStr">
         <is>
-          <t>Operating expense</t>
+          <t>Cash taxes LTM</t>
         </is>
       </c>
       <c r="H109" s="44" t="n">
-        <v>11350</v>
+        <v>880000</v>
       </c>
       <c r="I109" s="27" t="inlineStr"/>
       <c r="J109" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K109" s="27" t="inlineStr">
@@ -9403,17 +9407,17 @@
     <row r="110">
       <c r="A110" s="36" t="inlineStr">
         <is>
-          <t>RPT-00236</t>
+          <t>RPT-072X05</t>
         </is>
       </c>
       <c r="B110" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C110" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Approved lender metric basis</t>
         </is>
       </c>
       <c r="D110" s="27" t="inlineStr">
@@ -9423,7 +9427,7 @@
       </c>
       <c r="E110" s="27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>LTM 2026-06-30</t>
         </is>
       </c>
       <c r="F110" s="27" t="inlineStr">
@@ -9433,11 +9437,11 @@
       </c>
       <c r="G110" s="27" t="inlineStr">
         <is>
-          <t>Free cash flow</t>
+          <t>Maintenance capex LTM</t>
         </is>
       </c>
       <c r="H110" s="44" t="n">
-        <v>2850000</v>
+        <v>1250000</v>
       </c>
       <c r="I110" s="27" t="inlineStr"/>
       <c r="J110" s="27" t="inlineStr">
@@ -9460,17 +9464,17 @@
     <row r="111">
       <c r="A111" s="36" t="inlineStr">
         <is>
-          <t>RPT-00237</t>
+          <t>RPT-072X06</t>
         </is>
       </c>
       <c r="B111" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C111" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Approved lender metric basis</t>
         </is>
       </c>
       <c r="D111" s="27" t="inlineStr">
@@ -9480,7 +9484,7 @@
       </c>
       <c r="E111" s="27" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>LTM 2026-06-30</t>
         </is>
       </c>
       <c r="F111" s="27" t="inlineStr">
@@ -9490,16 +9494,16 @@
       </c>
       <c r="G111" s="27" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Distributions LTM</t>
         </is>
       </c>
       <c r="H111" s="44" t="n">
-        <v>0.5</v>
+        <v>400000</v>
       </c>
       <c r="I111" s="27" t="inlineStr"/>
       <c r="J111" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K111" s="27" t="inlineStr">
@@ -9517,17 +9521,17 @@
     <row r="112">
       <c r="A112" s="36" t="inlineStr">
         <is>
-          <t>RPT-00238</t>
+          <t>RPT-072X07</t>
         </is>
       </c>
       <c r="B112" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C112" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Signed guidance decision</t>
         </is>
       </c>
       <c r="D112" s="27" t="inlineStr">
@@ -9537,7 +9541,7 @@
       </c>
       <c r="E112" s="27" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F112" s="27" t="inlineStr">
@@ -9547,16 +9551,16 @@
       </c>
       <c r="G112" s="27" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Revenue guidance low</t>
         </is>
       </c>
       <c r="H112" s="44" t="n">
-        <v>52400000</v>
+        <v>52000</v>
       </c>
       <c r="I112" s="27" t="inlineStr"/>
       <c r="J112" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K112" s="27" t="inlineStr">
@@ -9574,17 +9578,17 @@
     <row r="113">
       <c r="A113" s="36" t="inlineStr">
         <is>
-          <t>RPT-00239</t>
+          <t>RPT-072X08</t>
         </is>
       </c>
       <c r="B113" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C113" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Signed guidance decision</t>
         </is>
       </c>
       <c r="D113" s="27" t="inlineStr">
@@ -9594,7 +9598,7 @@
       </c>
       <c r="E113" s="27" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F113" s="27" t="inlineStr">
@@ -9604,16 +9608,16 @@
       </c>
       <c r="G113" s="27" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Revenue guidance high</t>
         </is>
       </c>
       <c r="H113" s="44" t="n">
-        <v>0.278</v>
+        <v>55000000</v>
       </c>
       <c r="I113" s="27" t="inlineStr"/>
       <c r="J113" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K113" s="27" t="inlineStr">
@@ -9631,17 +9635,17 @@
     <row r="114">
       <c r="A114" s="36" t="inlineStr">
         <is>
-          <t>RPT-00240</t>
+          <t>RPT-072X09</t>
         </is>
       </c>
       <c r="B114" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C114" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Signed guidance decision</t>
         </is>
       </c>
       <c r="D114" s="27" t="inlineStr">
@@ -9651,7 +9655,7 @@
       </c>
       <c r="E114" s="27" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F114" s="27" t="inlineStr">
@@ -9661,11 +9665,11 @@
       </c>
       <c r="G114" s="27" t="inlineStr">
         <is>
-          <t>Operating expense</t>
+          <t>EBITDA guidance low</t>
         </is>
       </c>
       <c r="H114" s="44" t="n">
-        <v>11520000</v>
+        <v>3000000</v>
       </c>
       <c r="I114" s="27" t="inlineStr"/>
       <c r="J114" s="27" t="inlineStr">
@@ -9688,17 +9692,17 @@
     <row r="115">
       <c r="A115" s="36" t="inlineStr">
         <is>
-          <t>RPT-00241</t>
+          <t>RPT-072X10</t>
         </is>
       </c>
       <c r="B115" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C115" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Signed guidance decision</t>
         </is>
       </c>
       <c r="D115" s="27" t="inlineStr">
@@ -9708,7 +9712,7 @@
       </c>
       <c r="E115" s="27" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F115" s="27" t="inlineStr">
@@ -9718,11 +9722,11 @@
       </c>
       <c r="G115" s="27" t="inlineStr">
         <is>
-          <t>Free cash flow</t>
+          <t>EBITDA guidance high</t>
         </is>
       </c>
       <c r="H115" s="44" t="n">
-        <v>3650000</v>
+        <v>4250000</v>
       </c>
       <c r="I115" s="27" t="inlineStr"/>
       <c r="J115" s="27" t="inlineStr">
@@ -9745,17 +9749,17 @@
     <row r="116">
       <c r="A116" s="36" t="inlineStr">
         <is>
-          <t>RPT-00242</t>
+          <t>RPT-072X11</t>
         </is>
       </c>
       <c r="B116" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C116" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Signed guidance decision</t>
         </is>
       </c>
       <c r="D116" s="27" t="inlineStr">
@@ -9765,7 +9769,7 @@
       </c>
       <c r="E116" s="27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F116" s="27" t="inlineStr">
@@ -9775,16 +9779,16 @@
       </c>
       <c r="G116" s="27" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Signed combined stress EBITDA</t>
         </is>
       </c>
       <c r="H116" s="44" t="n">
-        <v>0.3</v>
+        <v>2811.47535</v>
       </c>
       <c r="I116" s="27" t="inlineStr"/>
       <c r="J116" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K116" s="27" t="inlineStr">
@@ -9802,17 +9806,17 @@
     <row r="117">
       <c r="A117" s="36" t="inlineStr">
         <is>
-          <t>RPT-00243</t>
+          <t>RPT-072X12</t>
         </is>
       </c>
       <c r="B117" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C117" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Signed guidance decision</t>
         </is>
       </c>
       <c r="D117" s="27" t="inlineStr">
@@ -9822,7 +9826,7 @@
       </c>
       <c r="E117" s="27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F117" s="27" t="inlineStr">
@@ -9832,16 +9836,16 @@
       </c>
       <c r="G117" s="27" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Guidance update EBITDA buffer</t>
         </is>
       </c>
       <c r="H117" s="44" t="n">
-        <v>54600</v>
+        <v>250000</v>
       </c>
       <c r="I117" s="27" t="inlineStr"/>
       <c r="J117" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K117" s="27" t="inlineStr">
@@ -9859,17 +9863,17 @@
     <row r="118">
       <c r="A118" s="36" t="inlineStr">
         <is>
-          <t>RPT-00244</t>
+          <t>RPT-072X13</t>
         </is>
       </c>
       <c r="B118" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C118" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Signed guidance decision</t>
         </is>
       </c>
       <c r="D118" s="27" t="inlineStr">
@@ -9879,7 +9883,7 @@
       </c>
       <c r="E118" s="27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F118" s="27" t="inlineStr">
@@ -9889,11 +9893,11 @@
       </c>
       <c r="G118" s="27" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Stress contribution per revenue dollar</t>
         </is>
       </c>
       <c r="H118" s="44" t="n">
-        <v>0.291</v>
+        <v>0.0945</v>
       </c>
       <c r="I118" s="27" t="inlineStr"/>
       <c r="J118" s="27" t="inlineStr">
@@ -9916,17 +9920,17 @@
     <row r="119">
       <c r="A119" s="36" t="inlineStr">
         <is>
-          <t>RPT-00245</t>
+          <t>RPT-072X14</t>
         </is>
       </c>
       <c r="B119" s="27" t="inlineStr">
         <is>
-          <t>Earnings guidance range and probability bridge</t>
+          <t>Create the Q2 earnings and lender narrative</t>
         </is>
       </c>
       <c r="C119" s="27" t="inlineStr">
         <is>
-          <t>Guidance scenarios</t>
+          <t>Signed guidance decision</t>
         </is>
       </c>
       <c r="D119" s="27" t="inlineStr">
@@ -9936,7 +9940,7 @@
       </c>
       <c r="E119" s="27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F119" s="27" t="inlineStr">
@@ -9946,16 +9950,18 @@
       </c>
       <c r="G119" s="27" t="inlineStr">
         <is>
-          <t>Operating expense</t>
-        </is>
-      </c>
-      <c r="H119" s="44" t="n">
-        <v>11680000</v>
-      </c>
-      <c r="I119" s="27" t="inlineStr"/>
+          <t>Largest downside driver</t>
+        </is>
+      </c>
+      <c r="H119" s="44" t="inlineStr"/>
+      <c r="I119" s="27" t="inlineStr">
+        <is>
+          <t>Copper escalation</t>
+        </is>
+      </c>
       <c r="J119" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K119" s="27" t="inlineStr">
@@ -9973,7 +9979,7 @@
     <row r="120">
       <c r="A120" s="36" t="inlineStr">
         <is>
-          <t>RPT-00246</t>
+          <t>RPT-00232</t>
         </is>
       </c>
       <c r="B120" s="27" t="inlineStr">
@@ -9993,7 +9999,7 @@
       </c>
       <c r="E120" s="27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F120" s="27" t="inlineStr">
@@ -10003,16 +10009,16 @@
       </c>
       <c r="G120" s="27" t="inlineStr">
         <is>
-          <t>Free cash flow</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="H120" s="44" t="n">
-        <v>4150000</v>
+        <v>0.2</v>
       </c>
       <c r="I120" s="27" t="inlineStr"/>
       <c r="J120" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K120" s="27" t="inlineStr">
@@ -10030,7 +10036,7 @@
     <row r="121">
       <c r="A121" s="36" t="inlineStr">
         <is>
-          <t>RPT-00247</t>
+          <t>RPT-00233</t>
         </is>
       </c>
       <c r="B121" s="27" t="inlineStr">
@@ -10040,17 +10046,17 @@
       </c>
       <c r="C121" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D121" s="27" t="inlineStr">
         <is>
-          <t>Helix schedule slip</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E121" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F121" s="27" t="inlineStr">
@@ -10060,16 +10066,16 @@
       </c>
       <c r="G121" s="27" t="inlineStr">
         <is>
-          <t>Revenue impact</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="H121" s="44" t="n">
-        <v>-1100</v>
+        <v>49800000</v>
       </c>
       <c r="I121" s="27" t="inlineStr"/>
       <c r="J121" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K121" s="27" t="inlineStr">
@@ -10087,7 +10093,7 @@
     <row r="122">
       <c r="A122" s="36" t="inlineStr">
         <is>
-          <t>RPT-00248</t>
+          <t>RPT-00234</t>
         </is>
       </c>
       <c r="B122" s="27" t="inlineStr">
@@ -10097,17 +10103,17 @@
       </c>
       <c r="C122" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D122" s="27" t="inlineStr">
         <is>
-          <t>Helix schedule slip</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E122" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F122" s="27" t="inlineStr">
@@ -10117,16 +10123,16 @@
       </c>
       <c r="G122" s="27" t="inlineStr">
         <is>
-          <t>EBITDA impact</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="H122" s="44" t="n">
-        <v>-420000</v>
+        <v>0.26</v>
       </c>
       <c r="I122" s="27" t="inlineStr"/>
       <c r="J122" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K122" s="27" t="inlineStr">
@@ -10144,7 +10150,7 @@
     <row r="123">
       <c r="A123" s="36" t="inlineStr">
         <is>
-          <t>RPT-00249</t>
+          <t>RPT-00235</t>
         </is>
       </c>
       <c r="B123" s="27" t="inlineStr">
@@ -10154,17 +10160,17 @@
       </c>
       <c r="C123" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D123" s="27" t="inlineStr">
         <is>
-          <t>Helix schedule slip</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E123" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F123" s="27" t="inlineStr">
@@ -10174,16 +10180,16 @@
       </c>
       <c r="G123" s="27" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Operating expense</t>
         </is>
       </c>
       <c r="H123" s="44" t="n">
-        <v>0.35</v>
+        <v>11350</v>
       </c>
       <c r="I123" s="27" t="inlineStr"/>
       <c r="J123" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K123" s="27" t="inlineStr">
@@ -10201,7 +10207,7 @@
     <row r="124">
       <c r="A124" s="36" t="inlineStr">
         <is>
-          <t>RPT-00250</t>
+          <t>RPT-00236</t>
         </is>
       </c>
       <c r="B124" s="27" t="inlineStr">
@@ -10211,17 +10217,17 @@
       </c>
       <c r="C124" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D124" s="27" t="inlineStr">
         <is>
-          <t>Service renewal upside</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E124" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F124" s="27" t="inlineStr">
@@ -10231,11 +10237,11 @@
       </c>
       <c r="G124" s="27" t="inlineStr">
         <is>
-          <t>Revenue impact</t>
+          <t>Free cash flow</t>
         </is>
       </c>
       <c r="H124" s="44" t="n">
-        <v>620000</v>
+        <v>2850000</v>
       </c>
       <c r="I124" s="27" t="inlineStr"/>
       <c r="J124" s="27" t="inlineStr">
@@ -10258,7 +10264,7 @@
     <row r="125">
       <c r="A125" s="36" t="inlineStr">
         <is>
-          <t>RPT-00251</t>
+          <t>RPT-00237</t>
         </is>
       </c>
       <c r="B125" s="27" t="inlineStr">
@@ -10268,17 +10274,17 @@
       </c>
       <c r="C125" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D125" s="27" t="inlineStr">
         <is>
-          <t>Service renewal upside</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E125" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="F125" s="27" t="inlineStr">
@@ -10288,16 +10294,16 @@
       </c>
       <c r="G125" s="27" t="inlineStr">
         <is>
-          <t>EBITDA impact</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="H125" s="44" t="n">
-        <v>330</v>
+        <v>0.5</v>
       </c>
       <c r="I125" s="27" t="inlineStr"/>
       <c r="J125" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K125" s="27" t="inlineStr">
@@ -10315,7 +10321,7 @@
     <row r="126">
       <c r="A126" s="36" t="inlineStr">
         <is>
-          <t>RPT-00252</t>
+          <t>RPT-00238</t>
         </is>
       </c>
       <c r="B126" s="27" t="inlineStr">
@@ -10325,17 +10331,17 @@
       </c>
       <c r="C126" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D126" s="27" t="inlineStr">
         <is>
-          <t>Service renewal upside</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E126" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="F126" s="27" t="inlineStr">
@@ -10345,16 +10351,16 @@
       </c>
       <c r="G126" s="27" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="H126" s="44" t="n">
-        <v>0.55</v>
+        <v>52400000</v>
       </c>
       <c r="I126" s="27" t="inlineStr"/>
       <c r="J126" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K126" s="27" t="inlineStr">
@@ -10372,7 +10378,7 @@
     <row r="127">
       <c r="A127" s="36" t="inlineStr">
         <is>
-          <t>RPT-00253</t>
+          <t>RPT-00239</t>
         </is>
       </c>
       <c r="B127" s="27" t="inlineStr">
@@ -10382,17 +10388,17 @@
       </c>
       <c r="C127" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D127" s="27" t="inlineStr">
         <is>
-          <t>Copper escalation</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E127" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="F127" s="27" t="inlineStr">
@@ -10402,16 +10408,16 @@
       </c>
       <c r="G127" s="27" t="inlineStr">
         <is>
-          <t>Revenue impact</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="H127" s="44" t="n">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="I127" s="27" t="inlineStr"/>
       <c r="J127" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K127" s="27" t="inlineStr">
@@ -10429,7 +10435,7 @@
     <row r="128">
       <c r="A128" s="36" t="inlineStr">
         <is>
-          <t>RPT-00254</t>
+          <t>RPT-00240</t>
         </is>
       </c>
       <c r="B128" s="27" t="inlineStr">
@@ -10439,17 +10445,17 @@
       </c>
       <c r="C128" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D128" s="27" t="inlineStr">
         <is>
-          <t>Copper escalation</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E128" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="F128" s="27" t="inlineStr">
@@ -10459,11 +10465,11 @@
       </c>
       <c r="G128" s="27" t="inlineStr">
         <is>
-          <t>EBITDA impact</t>
+          <t>Operating expense</t>
         </is>
       </c>
       <c r="H128" s="44" t="n">
-        <v>-280000</v>
+        <v>11520000</v>
       </c>
       <c r="I128" s="27" t="inlineStr"/>
       <c r="J128" s="27" t="inlineStr">
@@ -10486,7 +10492,7 @@
     <row r="129">
       <c r="A129" s="36" t="inlineStr">
         <is>
-          <t>RPT-00255</t>
+          <t>RPT-00241</t>
         </is>
       </c>
       <c r="B129" s="27" t="inlineStr">
@@ -10496,17 +10502,17 @@
       </c>
       <c r="C129" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D129" s="27" t="inlineStr">
         <is>
-          <t>Copper escalation</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E129" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="F129" s="27" t="inlineStr">
@@ -10516,16 +10522,16 @@
       </c>
       <c r="G129" s="27" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Free cash flow</t>
         </is>
       </c>
       <c r="H129" s="44" t="n">
-        <v>0.65</v>
+        <v>3650000</v>
       </c>
       <c r="I129" s="27" t="inlineStr"/>
       <c r="J129" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K129" s="27" t="inlineStr">
@@ -10543,7 +10549,7 @@
     <row r="130">
       <c r="A130" s="36" t="inlineStr">
         <is>
-          <t>RPT-00256</t>
+          <t>RPT-00242</t>
         </is>
       </c>
       <c r="B130" s="27" t="inlineStr">
@@ -10553,17 +10559,17 @@
       </c>
       <c r="C130" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D130" s="27" t="inlineStr">
         <is>
-          <t>Controls commissioning</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E130" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F130" s="27" t="inlineStr">
@@ -10573,16 +10579,16 @@
       </c>
       <c r="G130" s="27" t="inlineStr">
         <is>
-          <t>Revenue impact</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="H130" s="44" t="n">
-        <v>450000</v>
+        <v>0.3</v>
       </c>
       <c r="I130" s="27" t="inlineStr"/>
       <c r="J130" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K130" s="27" t="inlineStr">
@@ -10600,7 +10606,7 @@
     <row r="131">
       <c r="A131" s="36" t="inlineStr">
         <is>
-          <t>RPT-00257</t>
+          <t>RPT-00243</t>
         </is>
       </c>
       <c r="B131" s="27" t="inlineStr">
@@ -10610,17 +10616,17 @@
       </c>
       <c r="C131" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D131" s="27" t="inlineStr">
         <is>
-          <t>Controls commissioning</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E131" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F131" s="27" t="inlineStr">
@@ -10630,16 +10636,16 @@
       </c>
       <c r="G131" s="27" t="inlineStr">
         <is>
-          <t>EBITDA impact</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="H131" s="44" t="n">
-        <v>190000</v>
+        <v>54600</v>
       </c>
       <c r="I131" s="27" t="inlineStr"/>
       <c r="J131" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K131" s="27" t="inlineStr">
@@ -10657,7 +10663,7 @@
     <row r="132">
       <c r="A132" s="36" t="inlineStr">
         <is>
-          <t>RPT-00258</t>
+          <t>RPT-00244</t>
         </is>
       </c>
       <c r="B132" s="27" t="inlineStr">
@@ -10667,17 +10673,17 @@
       </c>
       <c r="C132" s="27" t="inlineStr">
         <is>
-          <t>Guidance risk register</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D132" s="27" t="inlineStr">
         <is>
-          <t>Controls commissioning</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E132" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F132" s="27" t="inlineStr">
@@ -10687,11 +10693,11 @@
       </c>
       <c r="G132" s="27" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="H132" s="44" t="n">
-        <v>0.6</v>
+        <v>0.291</v>
       </c>
       <c r="I132" s="27" t="inlineStr"/>
       <c r="J132" s="27" t="inlineStr">
@@ -10714,7 +10720,7 @@
     <row r="133">
       <c r="A133" s="36" t="inlineStr">
         <is>
-          <t>RPT-00259</t>
+          <t>RPT-00245</t>
         </is>
       </c>
       <c r="B133" s="27" t="inlineStr">
@@ -10724,7 +10730,7 @@
       </c>
       <c r="C133" s="27" t="inlineStr">
         <is>
-          <t>Investor guidance policy</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D133" s="27" t="inlineStr">
@@ -10734,7 +10740,7 @@
       </c>
       <c r="E133" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F133" s="27" t="inlineStr">
@@ -10744,16 +10750,16 @@
       </c>
       <c r="G133" s="27" t="inlineStr">
         <is>
-          <t>Minimum guidance confidence</t>
+          <t>Operating expense</t>
         </is>
       </c>
       <c r="H133" s="44" t="n">
-        <v>0.7</v>
+        <v>11680000</v>
       </c>
       <c r="I133" s="27" t="inlineStr"/>
       <c r="J133" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K133" s="27" t="inlineStr">
@@ -10771,7 +10777,7 @@
     <row r="134">
       <c r="A134" s="36" t="inlineStr">
         <is>
-          <t>RPT-00260</t>
+          <t>RPT-00246</t>
         </is>
       </c>
       <c r="B134" s="27" t="inlineStr">
@@ -10781,7 +10787,7 @@
       </c>
       <c r="C134" s="27" t="inlineStr">
         <is>
-          <t>Investor guidance policy</t>
+          <t>Guidance scenarios</t>
         </is>
       </c>
       <c r="D134" s="27" t="inlineStr">
@@ -10791,7 +10797,7 @@
       </c>
       <c r="E134" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F134" s="27" t="inlineStr">
@@ -10801,11 +10807,11 @@
       </c>
       <c r="G134" s="27" t="inlineStr">
         <is>
-          <t>Revenue rounding increment</t>
+          <t>Free cash flow</t>
         </is>
       </c>
       <c r="H134" s="44" t="n">
-        <v>500000</v>
+        <v>4150000</v>
       </c>
       <c r="I134" s="27" t="inlineStr"/>
       <c r="J134" s="27" t="inlineStr">
@@ -10828,7 +10834,7 @@
     <row r="135">
       <c r="A135" s="36" t="inlineStr">
         <is>
-          <t>RPT-00261</t>
+          <t>RPT-00247</t>
         </is>
       </c>
       <c r="B135" s="27" t="inlineStr">
@@ -10838,12 +10844,12 @@
       </c>
       <c r="C135" s="27" t="inlineStr">
         <is>
-          <t>Investor guidance policy</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D135" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Helix schedule slip</t>
         </is>
       </c>
       <c r="E135" s="27" t="inlineStr">
@@ -10858,16 +10864,16 @@
       </c>
       <c r="G135" s="27" t="inlineStr">
         <is>
-          <t>EBITDA rounding increment</t>
+          <t>Revenue impact</t>
         </is>
       </c>
       <c r="H135" s="44" t="n">
-        <v>250000</v>
+        <v>-1100</v>
       </c>
       <c r="I135" s="27" t="inlineStr"/>
       <c r="J135" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K135" s="27" t="inlineStr">
@@ -10885,7 +10891,7 @@
     <row r="136">
       <c r="A136" s="36" t="inlineStr">
         <is>
-          <t>RPT-00262</t>
+          <t>RPT-00248</t>
         </is>
       </c>
       <c r="B136" s="27" t="inlineStr">
@@ -10895,12 +10901,12 @@
       </c>
       <c r="C136" s="27" t="inlineStr">
         <is>
-          <t>Investor guidance policy</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D136" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Helix schedule slip</t>
         </is>
       </c>
       <c r="E136" s="27" t="inlineStr">
@@ -10915,18 +10921,16 @@
       </c>
       <c r="G136" s="27" t="inlineStr">
         <is>
-          <t>Interval selection metric</t>
-        </is>
-      </c>
-      <c r="H136" s="44" t="inlineStr"/>
-      <c r="I136" s="27" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
+          <t>EBITDA impact</t>
+        </is>
+      </c>
+      <c r="H136" s="44" t="n">
+        <v>-420000</v>
+      </c>
+      <c r="I136" s="27" t="inlineStr"/>
       <c r="J136" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K136" s="27" t="inlineStr">
@@ -10944,7 +10948,7 @@
     <row r="137">
       <c r="A137" s="36" t="inlineStr">
         <is>
-          <t>RPT-00277</t>
+          <t>RPT-00249</t>
         </is>
       </c>
       <c r="B137" s="27" t="inlineStr">
@@ -10954,12 +10958,12 @@
       </c>
       <c r="C137" s="27" t="inlineStr">
         <is>
-          <t>Guidance combined stress</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D137" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Helix schedule slip</t>
         </is>
       </c>
       <c r="E137" s="27" t="inlineStr">
@@ -10974,11 +10978,11 @@
       </c>
       <c r="G137" s="27" t="inlineStr">
         <is>
-          <t>Incremental revenue shock</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="H137" s="44" t="n">
-        <v>-0.01</v>
+        <v>0.35</v>
       </c>
       <c r="I137" s="27" t="inlineStr"/>
       <c r="J137" s="27" t="inlineStr">
@@ -11001,7 +11005,7 @@
     <row r="138">
       <c r="A138" s="36" t="inlineStr">
         <is>
-          <t>RPT-00278</t>
+          <t>RPT-00250</t>
         </is>
       </c>
       <c r="B138" s="27" t="inlineStr">
@@ -11011,12 +11015,12 @@
       </c>
       <c r="C138" s="27" t="inlineStr">
         <is>
-          <t>Guidance combined stress</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D138" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Service renewal upside</t>
         </is>
       </c>
       <c r="E138" s="27" t="inlineStr">
@@ -11031,16 +11035,16 @@
       </c>
       <c r="G138" s="27" t="inlineStr">
         <is>
-          <t>Incremental gross margin shock</t>
+          <t>Revenue impact</t>
         </is>
       </c>
       <c r="H138" s="44" t="n">
-        <v>-0.0035</v>
+        <v>620000</v>
       </c>
       <c r="I138" s="27" t="inlineStr"/>
       <c r="J138" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K138" s="27" t="inlineStr">
@@ -11058,7 +11062,7 @@
     <row r="139">
       <c r="A139" s="36" t="inlineStr">
         <is>
-          <t>RPT-00279</t>
+          <t>RPT-00251</t>
         </is>
       </c>
       <c r="B139" s="27" t="inlineStr">
@@ -11068,12 +11072,12 @@
       </c>
       <c r="C139" s="27" t="inlineStr">
         <is>
-          <t>Guidance combined stress</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D139" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Service renewal upside</t>
         </is>
       </c>
       <c r="E139" s="27" t="inlineStr">
@@ -11088,16 +11092,16 @@
       </c>
       <c r="G139" s="27" t="inlineStr">
         <is>
-          <t>Variable opex response percent</t>
+          <t>EBITDA impact</t>
         </is>
       </c>
       <c r="H139" s="44" t="n">
-        <v>0.18</v>
+        <v>330</v>
       </c>
       <c r="I139" s="27" t="inlineStr"/>
       <c r="J139" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K139" s="27" t="inlineStr">
@@ -11115,7 +11119,7 @@
     <row r="140">
       <c r="A140" s="36" t="inlineStr">
         <is>
-          <t>RPT-00280</t>
+          <t>RPT-00252</t>
         </is>
       </c>
       <c r="B140" s="27" t="inlineStr">
@@ -11125,12 +11129,12 @@
       </c>
       <c r="C140" s="27" t="inlineStr">
         <is>
-          <t>Guidance combined stress</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D140" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Service renewal upside</t>
         </is>
       </c>
       <c r="E140" s="27" t="inlineStr">
@@ -11145,11 +11149,11 @@
       </c>
       <c r="G140" s="27" t="inlineStr">
         <is>
-          <t>Stress cash conversion percent</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="H140" s="44" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="I140" s="27" t="inlineStr"/>
       <c r="J140" s="27" t="inlineStr">
@@ -11172,7 +11176,7 @@
     <row r="141">
       <c r="A141" s="36" t="inlineStr">
         <is>
-          <t>RPT-00281</t>
+          <t>RPT-00253</t>
         </is>
       </c>
       <c r="B141" s="27" t="inlineStr">
@@ -11182,12 +11186,12 @@
       </c>
       <c r="C141" s="27" t="inlineStr">
         <is>
-          <t>Guidance combined stress</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D141" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Copper escalation</t>
         </is>
       </c>
       <c r="E141" s="27" t="inlineStr">
@@ -11202,11 +11206,11 @@
       </c>
       <c r="G141" s="27" t="inlineStr">
         <is>
-          <t>Guidance update EBITDA buffer</t>
+          <t>Revenue impact</t>
         </is>
       </c>
       <c r="H141" s="44" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="I141" s="27" t="inlineStr"/>
       <c r="J141" s="27" t="inlineStr">
@@ -11229,7 +11233,7 @@
     <row r="142">
       <c r="A142" s="36" t="inlineStr">
         <is>
-          <t>RPT-00282</t>
+          <t>RPT-00254</t>
         </is>
       </c>
       <c r="B142" s="27" t="inlineStr">
@@ -11239,12 +11243,12 @@
       </c>
       <c r="C142" s="27" t="inlineStr">
         <is>
-          <t>Guidance combined stress</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D142" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Copper escalation</t>
         </is>
       </c>
       <c r="E142" s="27" t="inlineStr">
@@ -11259,18 +11263,16 @@
       </c>
       <c r="G142" s="27" t="inlineStr">
         <is>
-          <t>Starting scenario</t>
-        </is>
-      </c>
-      <c r="H142" s="44" t="inlineStr"/>
-      <c r="I142" s="27" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
+          <t>EBITDA impact</t>
+        </is>
+      </c>
+      <c r="H142" s="44" t="n">
+        <v>-280000</v>
+      </c>
+      <c r="I142" s="27" t="inlineStr"/>
       <c r="J142" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K142" s="27" t="inlineStr">
@@ -11288,7 +11290,7 @@
     <row r="143">
       <c r="A143" s="36" t="inlineStr">
         <is>
-          <t>RPT-00283</t>
+          <t>RPT-00255</t>
         </is>
       </c>
       <c r="B143" s="27" t="inlineStr">
@@ -11298,12 +11300,12 @@
       </c>
       <c r="C143" s="27" t="inlineStr">
         <is>
-          <t>Guidance combined stress</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D143" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Copper escalation</t>
         </is>
       </c>
       <c r="E143" s="27" t="inlineStr">
@@ -11318,18 +11320,16 @@
       </c>
       <c r="G143" s="27" t="inlineStr">
         <is>
-          <t>Revenue risk inclusion</t>
-        </is>
-      </c>
-      <c r="H143" s="44" t="inlineStr"/>
-      <c r="I143" s="27" t="inlineStr">
-        <is>
-          <t>All risk-register revenue impacts at full signed face value</t>
-        </is>
-      </c>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="H143" s="44" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I143" s="27" t="inlineStr"/>
       <c r="J143" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K143" s="27" t="inlineStr">
@@ -11347,7 +11347,7 @@
     <row r="144">
       <c r="A144" s="36" t="inlineStr">
         <is>
-          <t>RPT-00284</t>
+          <t>RPT-00256</t>
         </is>
       </c>
       <c r="B144" s="27" t="inlineStr">
@@ -11357,12 +11357,12 @@
       </c>
       <c r="C144" s="27" t="inlineStr">
         <is>
-          <t>Guidance combined stress</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D144" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Controls commissioning</t>
         </is>
       </c>
       <c r="E144" s="27" t="inlineStr">
@@ -11377,18 +11377,16 @@
       </c>
       <c r="G144" s="27" t="inlineStr">
         <is>
-          <t>EBITDA risk inclusion</t>
-        </is>
-      </c>
-      <c r="H144" s="44" t="inlineStr"/>
-      <c r="I144" s="27" t="inlineStr">
-        <is>
-          <t>Do not separately apply risk-register EBITDA impacts</t>
-        </is>
-      </c>
+          <t>Revenue impact</t>
+        </is>
+      </c>
+      <c r="H144" s="44" t="n">
+        <v>450000</v>
+      </c>
+      <c r="I144" s="27" t="inlineStr"/>
       <c r="J144" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K144" s="27" t="inlineStr">
@@ -11406,7 +11404,7 @@
     <row r="145">
       <c r="A145" s="36" t="inlineStr">
         <is>
-          <t>RPT-00285</t>
+          <t>RPT-00257</t>
         </is>
       </c>
       <c r="B145" s="27" t="inlineStr">
@@ -11416,12 +11414,12 @@
       </c>
       <c r="C145" s="27" t="inlineStr">
         <is>
-          <t>Guidance combined stress</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D145" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Controls commissioning</t>
         </is>
       </c>
       <c r="E145" s="27" t="inlineStr">
@@ -11436,18 +11434,16 @@
       </c>
       <c r="G145" s="27" t="inlineStr">
         <is>
-          <t>Opex response basis</t>
-        </is>
-      </c>
-      <c r="H145" s="44" t="inlineStr"/>
-      <c r="I145" s="27" t="inlineStr">
-        <is>
-          <t>Total revenue change from Base scenario</t>
-        </is>
-      </c>
+          <t>EBITDA impact</t>
+        </is>
+      </c>
+      <c r="H145" s="44" t="n">
+        <v>190000</v>
+      </c>
+      <c r="I145" s="27" t="inlineStr"/>
       <c r="J145" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K145" s="27" t="inlineStr">
@@ -11465,22 +11461,22 @@
     <row r="146">
       <c r="A146" s="36" t="inlineStr">
         <is>
-          <t>RPT-00349</t>
+          <t>RPT-00258</t>
         </is>
       </c>
       <c r="B146" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C146" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Guidance risk register</t>
         </is>
       </c>
       <c r="D146" s="27" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Controls commissioning</t>
         </is>
       </c>
       <c r="E146" s="27" t="inlineStr">
@@ -11495,16 +11491,16 @@
       </c>
       <c r="G146" s="27" t="inlineStr">
         <is>
-          <t>Forecast revenue</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="H146" s="44" t="n">
-        <v>31450000</v>
+        <v>0.6</v>
       </c>
       <c r="I146" s="27" t="inlineStr"/>
       <c r="J146" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K146" s="27" t="inlineStr">
@@ -11522,22 +11518,22 @@
     <row r="147">
       <c r="A147" s="36" t="inlineStr">
         <is>
-          <t>RPT-00350</t>
+          <t>RPT-00259</t>
         </is>
       </c>
       <c r="B147" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C147" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Investor guidance policy</t>
         </is>
       </c>
       <c r="D147" s="27" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E147" s="27" t="inlineStr">
@@ -11552,16 +11548,16 @@
       </c>
       <c r="G147" s="27" t="inlineStr">
         <is>
-          <t>Plan revenue</t>
+          <t>Minimum guidance confidence</t>
         </is>
       </c>
       <c r="H147" s="44" t="n">
-        <v>29900000</v>
+        <v>0.7</v>
       </c>
       <c r="I147" s="27" t="inlineStr"/>
       <c r="J147" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K147" s="27" t="inlineStr">
@@ -11579,22 +11575,22 @@
     <row r="148">
       <c r="A148" s="36" t="inlineStr">
         <is>
-          <t>RPT-00351</t>
+          <t>RPT-00260</t>
         </is>
       </c>
       <c r="B148" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C148" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Investor guidance policy</t>
         </is>
       </c>
       <c r="D148" s="27" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E148" s="27" t="inlineStr">
@@ -11609,16 +11605,16 @@
       </c>
       <c r="G148" s="27" t="inlineStr">
         <is>
-          <t>Forecast gross margin</t>
+          <t>Revenue rounding increment</t>
         </is>
       </c>
       <c r="H148" s="44" t="n">
-        <v>0.232</v>
+        <v>500000</v>
       </c>
       <c r="I148" s="27" t="inlineStr"/>
       <c r="J148" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K148" s="27" t="inlineStr">
@@ -11636,22 +11632,22 @@
     <row r="149">
       <c r="A149" s="36" t="inlineStr">
         <is>
-          <t>RPT-00352</t>
+          <t>RPT-00261</t>
         </is>
       </c>
       <c r="B149" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C149" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Investor guidance policy</t>
         </is>
       </c>
       <c r="D149" s="27" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E149" s="27" t="inlineStr">
@@ -11666,16 +11662,16 @@
       </c>
       <c r="G149" s="27" t="inlineStr">
         <is>
-          <t>Plan gross margin</t>
+          <t>EBITDA rounding increment</t>
         </is>
       </c>
       <c r="H149" s="44" t="n">
-        <v>0.245</v>
+        <v>250000</v>
       </c>
       <c r="I149" s="27" t="inlineStr"/>
       <c r="J149" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K149" s="27" t="inlineStr">
@@ -11693,22 +11689,22 @@
     <row r="150">
       <c r="A150" s="36" t="inlineStr">
         <is>
-          <t>RPT-00353</t>
+          <t>RPT-00262</t>
         </is>
       </c>
       <c r="B150" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C150" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Investor guidance policy</t>
         </is>
       </c>
       <c r="D150" s="27" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E150" s="27" t="inlineStr">
@@ -11723,16 +11719,18 @@
       </c>
       <c r="G150" s="27" t="inlineStr">
         <is>
-          <t>Forecast opex</t>
-        </is>
-      </c>
-      <c r="H150" s="44" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="I150" s="27" t="inlineStr"/>
+          <t>Interval selection metric</t>
+        </is>
+      </c>
+      <c r="H150" s="44" t="inlineStr"/>
+      <c r="I150" s="27" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
       <c r="J150" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K150" s="27" t="inlineStr">
@@ -11750,22 +11748,22 @@
     <row r="151">
       <c r="A151" s="36" t="inlineStr">
         <is>
-          <t>RPT-00354</t>
+          <t>RPT-00277</t>
         </is>
       </c>
       <c r="B151" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C151" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Guidance combined stress</t>
         </is>
       </c>
       <c r="D151" s="27" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E151" s="27" t="inlineStr">
@@ -11780,16 +11778,16 @@
       </c>
       <c r="G151" s="27" t="inlineStr">
         <is>
-          <t>Plan opex</t>
+          <t>Incremental revenue shock</t>
         </is>
       </c>
       <c r="H151" s="44" t="n">
-        <v>2050000</v>
+        <v>-0.01</v>
       </c>
       <c r="I151" s="27" t="inlineStr"/>
       <c r="J151" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K151" s="27" t="inlineStr">
@@ -11807,22 +11805,22 @@
     <row r="152">
       <c r="A152" s="36" t="inlineStr">
         <is>
-          <t>RPT-00355</t>
+          <t>RPT-00278</t>
         </is>
       </c>
       <c r="B152" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C152" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Guidance combined stress</t>
         </is>
       </c>
       <c r="D152" s="27" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E152" s="27" t="inlineStr">
@@ -11837,16 +11835,16 @@
       </c>
       <c r="G152" s="27" t="inlineStr">
         <is>
-          <t>Forecast revenue</t>
+          <t>Incremental gross margin shock</t>
         </is>
       </c>
       <c r="H152" s="44" t="n">
-        <v>14280000</v>
+        <v>-0.0035</v>
       </c>
       <c r="I152" s="27" t="inlineStr"/>
       <c r="J152" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K152" s="27" t="inlineStr">
@@ -11864,22 +11862,22 @@
     <row r="153">
       <c r="A153" s="36" t="inlineStr">
         <is>
-          <t>RPT-00356</t>
+          <t>RPT-00279</t>
         </is>
       </c>
       <c r="B153" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C153" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Guidance combined stress</t>
         </is>
       </c>
       <c r="D153" s="27" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E153" s="27" t="inlineStr">
@@ -11894,16 +11892,16 @@
       </c>
       <c r="G153" s="27" t="inlineStr">
         <is>
-          <t>Plan revenue</t>
+          <t>Variable opex response percent</t>
         </is>
       </c>
       <c r="H153" s="44" t="n">
-        <v>13650</v>
+        <v>0.18</v>
       </c>
       <c r="I153" s="27" t="inlineStr"/>
       <c r="J153" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K153" s="27" t="inlineStr">
@@ -11921,22 +11919,22 @@
     <row r="154">
       <c r="A154" s="36" t="inlineStr">
         <is>
-          <t>RPT-00357</t>
+          <t>RPT-00280</t>
         </is>
       </c>
       <c r="B154" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C154" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Guidance combined stress</t>
         </is>
       </c>
       <c r="D154" s="27" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E154" s="27" t="inlineStr">
@@ -11951,11 +11949,11 @@
       </c>
       <c r="G154" s="27" t="inlineStr">
         <is>
-          <t>Forecast gross margin</t>
+          <t>Stress cash conversion percent</t>
         </is>
       </c>
       <c r="H154" s="44" t="n">
-        <v>0.438</v>
+        <v>0.62</v>
       </c>
       <c r="I154" s="27" t="inlineStr"/>
       <c r="J154" s="27" t="inlineStr">
@@ -11978,22 +11976,22 @@
     <row r="155">
       <c r="A155" s="36" t="inlineStr">
         <is>
-          <t>RPT-00358</t>
+          <t>RPT-00281</t>
         </is>
       </c>
       <c r="B155" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C155" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Guidance combined stress</t>
         </is>
       </c>
       <c r="D155" s="27" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E155" s="27" t="inlineStr">
@@ -12008,16 +12006,16 @@
       </c>
       <c r="G155" s="27" t="inlineStr">
         <is>
-          <t>Plan gross margin</t>
+          <t>Guidance update EBITDA buffer</t>
         </is>
       </c>
       <c r="H155" s="44" t="n">
-        <v>0.425</v>
+        <v>250000</v>
       </c>
       <c r="I155" s="27" t="inlineStr"/>
       <c r="J155" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K155" s="27" t="inlineStr">
@@ -12035,22 +12033,22 @@
     <row r="156">
       <c r="A156" s="36" t="inlineStr">
         <is>
-          <t>RPT-00359</t>
+          <t>RPT-00282</t>
         </is>
       </c>
       <c r="B156" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C156" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Guidance combined stress</t>
         </is>
       </c>
       <c r="D156" s="27" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E156" s="27" t="inlineStr">
@@ -12065,16 +12063,18 @@
       </c>
       <c r="G156" s="27" t="inlineStr">
         <is>
-          <t>Forecast opex</t>
-        </is>
-      </c>
-      <c r="H156" s="44" t="n">
-        <v>2120000</v>
-      </c>
-      <c r="I156" s="27" t="inlineStr"/>
+          <t>Starting scenario</t>
+        </is>
+      </c>
+      <c r="H156" s="44" t="inlineStr"/>
+      <c r="I156" s="27" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
       <c r="J156" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K156" s="27" t="inlineStr">
@@ -12092,22 +12092,22 @@
     <row r="157">
       <c r="A157" s="36" t="inlineStr">
         <is>
-          <t>RPT-00360</t>
+          <t>RPT-00283</t>
         </is>
       </c>
       <c r="B157" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C157" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Guidance combined stress</t>
         </is>
       </c>
       <c r="D157" s="27" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E157" s="27" t="inlineStr">
@@ -12122,16 +12122,18 @@
       </c>
       <c r="G157" s="27" t="inlineStr">
         <is>
-          <t>Plan opex</t>
-        </is>
-      </c>
-      <c r="H157" s="44" t="n">
-        <v>1980</v>
-      </c>
-      <c r="I157" s="27" t="inlineStr"/>
+          <t>Revenue risk inclusion</t>
+        </is>
+      </c>
+      <c r="H157" s="44" t="inlineStr"/>
+      <c r="I157" s="27" t="inlineStr">
+        <is>
+          <t>All risk-register revenue impacts at full signed face value</t>
+        </is>
+      </c>
       <c r="J157" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K157" s="27" t="inlineStr">
@@ -12149,22 +12151,22 @@
     <row r="158">
       <c r="A158" s="36" t="inlineStr">
         <is>
-          <t>RPT-00361</t>
+          <t>RPT-00284</t>
         </is>
       </c>
       <c r="B158" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C158" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Guidance combined stress</t>
         </is>
       </c>
       <c r="D158" s="27" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E158" s="27" t="inlineStr">
@@ -12179,16 +12181,18 @@
       </c>
       <c r="G158" s="27" t="inlineStr">
         <is>
-          <t>Forecast revenue</t>
-        </is>
-      </c>
-      <c r="H158" s="44" t="n">
-        <v>7620000</v>
-      </c>
-      <c r="I158" s="27" t="inlineStr"/>
+          <t>EBITDA risk inclusion</t>
+        </is>
+      </c>
+      <c r="H158" s="44" t="inlineStr"/>
+      <c r="I158" s="27" t="inlineStr">
+        <is>
+          <t>Do not separately apply risk-register EBITDA impacts</t>
+        </is>
+      </c>
       <c r="J158" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K158" s="27" t="inlineStr">
@@ -12206,22 +12210,22 @@
     <row r="159">
       <c r="A159" s="36" t="inlineStr">
         <is>
-          <t>RPT-00362</t>
+          <t>RPT-00285</t>
         </is>
       </c>
       <c r="B159" s="27" t="inlineStr">
         <is>
-          <t>Create the CFO strategic-finance board deck</t>
+          <t>Earnings guidance range and probability bridge</t>
         </is>
       </c>
       <c r="C159" s="27" t="inlineStr">
         <is>
-          <t>Board operating outlook</t>
+          <t>Guidance combined stress</t>
         </is>
       </c>
       <c r="D159" s="27" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E159" s="27" t="inlineStr">
@@ -12236,16 +12240,18 @@
       </c>
       <c r="G159" s="27" t="inlineStr">
         <is>
-          <t>Plan revenue</t>
-        </is>
-      </c>
-      <c r="H159" s="44" t="n">
-        <v>7150000</v>
-      </c>
-      <c r="I159" s="27" t="inlineStr"/>
+          <t>Opex response basis</t>
+        </is>
+      </c>
+      <c r="H159" s="44" t="inlineStr"/>
+      <c r="I159" s="27" t="inlineStr">
+        <is>
+          <t>Total revenue change from Base scenario</t>
+        </is>
+      </c>
       <c r="J159" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K159" s="27" t="inlineStr">
@@ -12263,7 +12269,7 @@
     <row r="160">
       <c r="A160" s="36" t="inlineStr">
         <is>
-          <t>RPT-00363</t>
+          <t>RPT-00349</t>
         </is>
       </c>
       <c r="B160" s="27" t="inlineStr">
@@ -12278,7 +12284,7 @@
       </c>
       <c r="D160" s="27" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="E160" s="27" t="inlineStr">
@@ -12293,16 +12299,16 @@
       </c>
       <c r="G160" s="27" t="inlineStr">
         <is>
-          <t>Forecast gross margin</t>
+          <t>Forecast revenue</t>
         </is>
       </c>
       <c r="H160" s="44" t="n">
-        <v>0.295</v>
+        <v>31450000</v>
       </c>
       <c r="I160" s="27" t="inlineStr"/>
       <c r="J160" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K160" s="27" t="inlineStr">
@@ -12320,7 +12326,7 @@
     <row r="161">
       <c r="A161" s="36" t="inlineStr">
         <is>
-          <t>RPT-00364</t>
+          <t>RPT-00350</t>
         </is>
       </c>
       <c r="B161" s="27" t="inlineStr">
@@ -12335,7 +12341,7 @@
       </c>
       <c r="D161" s="27" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="E161" s="27" t="inlineStr">
@@ -12350,16 +12356,16 @@
       </c>
       <c r="G161" s="27" t="inlineStr">
         <is>
-          <t>Plan gross margin</t>
+          <t>Plan revenue</t>
         </is>
       </c>
       <c r="H161" s="44" t="n">
-        <v>0.328</v>
+        <v>29900000</v>
       </c>
       <c r="I161" s="27" t="inlineStr"/>
       <c r="J161" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K161" s="27" t="inlineStr">
@@ -12377,7 +12383,7 @@
     <row r="162">
       <c r="A162" s="36" t="inlineStr">
         <is>
-          <t>RPT-00365</t>
+          <t>RPT-00351</t>
         </is>
       </c>
       <c r="B162" s="27" t="inlineStr">
@@ -12392,7 +12398,7 @@
       </c>
       <c r="D162" s="27" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="E162" s="27" t="inlineStr">
@@ -12407,16 +12413,16 @@
       </c>
       <c r="G162" s="27" t="inlineStr">
         <is>
-          <t>Forecast opex</t>
+          <t>Forecast gross margin</t>
         </is>
       </c>
       <c r="H162" s="44" t="n">
-        <v>1060000</v>
+        <v>0.232</v>
       </c>
       <c r="I162" s="27" t="inlineStr"/>
       <c r="J162" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K162" s="27" t="inlineStr">
@@ -12434,7 +12440,7 @@
     <row r="163">
       <c r="A163" s="36" t="inlineStr">
         <is>
-          <t>RPT-00366</t>
+          <t>RPT-00352</t>
         </is>
       </c>
       <c r="B163" s="27" t="inlineStr">
@@ -12449,7 +12455,7 @@
       </c>
       <c r="D163" s="27" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="E163" s="27" t="inlineStr">
@@ -12464,16 +12470,16 @@
       </c>
       <c r="G163" s="27" t="inlineStr">
         <is>
-          <t>Plan opex</t>
+          <t>Plan gross margin</t>
         </is>
       </c>
       <c r="H163" s="44" t="n">
-        <v>1120000</v>
+        <v>0.245</v>
       </c>
       <c r="I163" s="27" t="inlineStr"/>
       <c r="J163" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K163" s="27" t="inlineStr">
@@ -12491,7 +12497,7 @@
     <row r="164">
       <c r="A164" s="36" t="inlineStr">
         <is>
-          <t>RPT-00367</t>
+          <t>RPT-00353</t>
         </is>
       </c>
       <c r="B164" s="27" t="inlineStr">
@@ -12501,17 +12507,17 @@
       </c>
       <c r="C164" s="27" t="inlineStr">
         <is>
-          <t>Board risk outlook</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D164" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="E164" s="27" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F164" s="27" t="inlineStr">
@@ -12521,11 +12527,11 @@
       </c>
       <c r="G164" s="27" t="inlineStr">
         <is>
-          <t>Covenant EBITDA</t>
+          <t>Forecast opex</t>
         </is>
       </c>
       <c r="H164" s="44" t="n">
-        <v>5520000</v>
+        <v>1850000</v>
       </c>
       <c r="I164" s="27" t="inlineStr"/>
       <c r="J164" s="27" t="inlineStr">
@@ -12548,7 +12554,7 @@
     <row r="165">
       <c r="A165" s="36" t="inlineStr">
         <is>
-          <t>RPT-00368</t>
+          <t>RPT-00354</t>
         </is>
       </c>
       <c r="B165" s="27" t="inlineStr">
@@ -12558,17 +12564,17 @@
       </c>
       <c r="C165" s="27" t="inlineStr">
         <is>
-          <t>Board risk outlook</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D165" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="E165" s="27" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F165" s="27" t="inlineStr">
@@ -12578,16 +12584,16 @@
       </c>
       <c r="G165" s="27" t="inlineStr">
         <is>
-          <t>Ending cash before financing</t>
+          <t>Plan opex</t>
         </is>
       </c>
       <c r="H165" s="44" t="n">
-        <v>3850</v>
+        <v>2050000</v>
       </c>
       <c r="I165" s="27" t="inlineStr"/>
       <c r="J165" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K165" s="27" t="inlineStr">
@@ -12605,7 +12611,7 @@
     <row r="166">
       <c r="A166" s="36" t="inlineStr">
         <is>
-          <t>RPT-00369</t>
+          <t>RPT-00355</t>
         </is>
       </c>
       <c r="B166" s="27" t="inlineStr">
@@ -12615,17 +12621,17 @@
       </c>
       <c r="C166" s="27" t="inlineStr">
         <is>
-          <t>Board risk outlook</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D166" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="E166" s="27" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F166" s="27" t="inlineStr">
@@ -12635,11 +12641,11 @@
       </c>
       <c r="G166" s="27" t="inlineStr">
         <is>
-          <t>Revolver balance</t>
+          <t>Forecast revenue</t>
         </is>
       </c>
       <c r="H166" s="44" t="n">
-        <v>2900000</v>
+        <v>14280000</v>
       </c>
       <c r="I166" s="27" t="inlineStr"/>
       <c r="J166" s="27" t="inlineStr">
@@ -12662,7 +12668,7 @@
     <row r="167">
       <c r="A167" s="36" t="inlineStr">
         <is>
-          <t>RPT-00370</t>
+          <t>RPT-00356</t>
         </is>
       </c>
       <c r="B167" s="27" t="inlineStr">
@@ -12672,17 +12678,17 @@
       </c>
       <c r="C167" s="27" t="inlineStr">
         <is>
-          <t>Board risk outlook</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D167" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="E167" s="27" t="inlineStr">
         <is>
-          <t>Downside</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F167" s="27" t="inlineStr">
@@ -12692,16 +12698,16 @@
       </c>
       <c r="G167" s="27" t="inlineStr">
         <is>
-          <t>Covenant EBITDA</t>
+          <t>Plan revenue</t>
         </is>
       </c>
       <c r="H167" s="44" t="n">
-        <v>3780000</v>
+        <v>13650</v>
       </c>
       <c r="I167" s="27" t="inlineStr"/>
       <c r="J167" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K167" s="27" t="inlineStr">
@@ -12719,7 +12725,7 @@
     <row r="168">
       <c r="A168" s="36" t="inlineStr">
         <is>
-          <t>RPT-00371</t>
+          <t>RPT-00357</t>
         </is>
       </c>
       <c r="B168" s="27" t="inlineStr">
@@ -12729,17 +12735,17 @@
       </c>
       <c r="C168" s="27" t="inlineStr">
         <is>
-          <t>Board risk outlook</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D168" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="E168" s="27" t="inlineStr">
         <is>
-          <t>Downside</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F168" s="27" t="inlineStr">
@@ -12749,16 +12755,16 @@
       </c>
       <c r="G168" s="27" t="inlineStr">
         <is>
-          <t>Ending cash before financing</t>
+          <t>Forecast gross margin</t>
         </is>
       </c>
       <c r="H168" s="44" t="n">
-        <v>1950000</v>
+        <v>0.438</v>
       </c>
       <c r="I168" s="27" t="inlineStr"/>
       <c r="J168" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K168" s="27" t="inlineStr">
@@ -12776,7 +12782,7 @@
     <row r="169">
       <c r="A169" s="36" t="inlineStr">
         <is>
-          <t>RPT-00372</t>
+          <t>RPT-00358</t>
         </is>
       </c>
       <c r="B169" s="27" t="inlineStr">
@@ -12786,17 +12792,17 @@
       </c>
       <c r="C169" s="27" t="inlineStr">
         <is>
-          <t>Board risk outlook</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D169" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="E169" s="27" t="inlineStr">
         <is>
-          <t>Downside</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F169" s="27" t="inlineStr">
@@ -12806,16 +12812,16 @@
       </c>
       <c r="G169" s="27" t="inlineStr">
         <is>
-          <t>Revolver balance</t>
+          <t>Plan gross margin</t>
         </is>
       </c>
       <c r="H169" s="44" t="n">
-        <v>4600</v>
+        <v>0.425</v>
       </c>
       <c r="I169" s="27" t="inlineStr"/>
       <c r="J169" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K169" s="27" t="inlineStr">
@@ -12833,7 +12839,7 @@
     <row r="170">
       <c r="A170" s="36" t="inlineStr">
         <is>
-          <t>RPT-00373</t>
+          <t>RPT-00359</t>
         </is>
       </c>
       <c r="B170" s="27" t="inlineStr">
@@ -12843,17 +12849,17 @@
       </c>
       <c r="C170" s="27" t="inlineStr">
         <is>
-          <t>Board risk outlook</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D170" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="E170" s="27" t="inlineStr">
         <is>
-          <t>Severe</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F170" s="27" t="inlineStr">
@@ -12863,11 +12869,11 @@
       </c>
       <c r="G170" s="27" t="inlineStr">
         <is>
-          <t>Covenant EBITDA</t>
+          <t>Forecast opex</t>
         </is>
       </c>
       <c r="H170" s="44" t="n">
-        <v>2650000</v>
+        <v>2120000</v>
       </c>
       <c r="I170" s="27" t="inlineStr"/>
       <c r="J170" s="27" t="inlineStr">
@@ -12890,7 +12896,7 @@
     <row r="171">
       <c r="A171" s="36" t="inlineStr">
         <is>
-          <t>RPT-00374</t>
+          <t>RPT-00360</t>
         </is>
       </c>
       <c r="B171" s="27" t="inlineStr">
@@ -12900,17 +12906,17 @@
       </c>
       <c r="C171" s="27" t="inlineStr">
         <is>
-          <t>Board risk outlook</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D171" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="E171" s="27" t="inlineStr">
         <is>
-          <t>Severe</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F171" s="27" t="inlineStr">
@@ -12920,16 +12926,16 @@
       </c>
       <c r="G171" s="27" t="inlineStr">
         <is>
-          <t>Ending cash before financing</t>
+          <t>Plan opex</t>
         </is>
       </c>
       <c r="H171" s="44" t="n">
-        <v>820000</v>
+        <v>1980</v>
       </c>
       <c r="I171" s="27" t="inlineStr"/>
       <c r="J171" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K171" s="27" t="inlineStr">
@@ -12947,7 +12953,7 @@
     <row r="172">
       <c r="A172" s="36" t="inlineStr">
         <is>
-          <t>RPT-00375</t>
+          <t>RPT-00361</t>
         </is>
       </c>
       <c r="B172" s="27" t="inlineStr">
@@ -12957,17 +12963,17 @@
       </c>
       <c r="C172" s="27" t="inlineStr">
         <is>
-          <t>Board risk outlook</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D172" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E172" s="27" t="inlineStr">
         <is>
-          <t>Severe</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F172" s="27" t="inlineStr">
@@ -12977,11 +12983,11 @@
       </c>
       <c r="G172" s="27" t="inlineStr">
         <is>
-          <t>Revolver balance</t>
+          <t>Forecast revenue</t>
         </is>
       </c>
       <c r="H172" s="44" t="n">
-        <v>6900000</v>
+        <v>7620000</v>
       </c>
       <c r="I172" s="27" t="inlineStr"/>
       <c r="J172" s="27" t="inlineStr">
@@ -13004,7 +13010,7 @@
     <row r="173">
       <c r="A173" s="36" t="inlineStr">
         <is>
-          <t>RPT-00376</t>
+          <t>RPT-00362</t>
         </is>
       </c>
       <c r="B173" s="27" t="inlineStr">
@@ -13014,17 +13020,17 @@
       </c>
       <c r="C173" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D173" s="27" t="inlineStr">
         <is>
-          <t>Procurement program</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E173" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F173" s="27" t="inlineStr">
@@ -13034,16 +13040,16 @@
       </c>
       <c r="G173" s="27" t="inlineStr">
         <is>
-          <t>Annual EBITDA impact</t>
+          <t>Plan revenue</t>
         </is>
       </c>
       <c r="H173" s="44" t="n">
-        <v>780</v>
+        <v>7150000</v>
       </c>
       <c r="I173" s="27" t="inlineStr"/>
       <c r="J173" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K173" s="27" t="inlineStr">
@@ -13061,7 +13067,7 @@
     <row r="174">
       <c r="A174" s="36" t="inlineStr">
         <is>
-          <t>RPT-00377</t>
+          <t>RPT-00363</t>
         </is>
       </c>
       <c r="B174" s="27" t="inlineStr">
@@ -13071,17 +13077,17 @@
       </c>
       <c r="C174" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D174" s="27" t="inlineStr">
         <is>
-          <t>Procurement program</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E174" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F174" s="27" t="inlineStr">
@@ -13091,11 +13097,11 @@
       </c>
       <c r="G174" s="27" t="inlineStr">
         <is>
-          <t>Realization probability</t>
+          <t>Forecast gross margin</t>
         </is>
       </c>
       <c r="H174" s="44" t="n">
-        <v>0.8</v>
+        <v>0.295</v>
       </c>
       <c r="I174" s="27" t="inlineStr"/>
       <c r="J174" s="27" t="inlineStr">
@@ -13118,7 +13124,7 @@
     <row r="175">
       <c r="A175" s="36" t="inlineStr">
         <is>
-          <t>RPT-00378</t>
+          <t>RPT-00364</t>
         </is>
       </c>
       <c r="B175" s="27" t="inlineStr">
@@ -13128,17 +13134,17 @@
       </c>
       <c r="C175" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D175" s="27" t="inlineStr">
         <is>
-          <t>Procurement program</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E175" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F175" s="27" t="inlineStr">
@@ -13148,18 +13154,16 @@
       </c>
       <c r="G175" s="27" t="inlineStr">
         <is>
-          <t>Management status</t>
-        </is>
-      </c>
-      <c r="H175" s="44" t="inlineStr"/>
-      <c r="I175" s="27" t="inlineStr">
-        <is>
-          <t>Approve</t>
-        </is>
-      </c>
+          <t>Plan gross margin</t>
+        </is>
+      </c>
+      <c r="H175" s="44" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="I175" s="27" t="inlineStr"/>
       <c r="J175" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K175" s="27" t="inlineStr">
@@ -13177,7 +13181,7 @@
     <row r="176">
       <c r="A176" s="36" t="inlineStr">
         <is>
-          <t>RPT-00379</t>
+          <t>RPT-00365</t>
         </is>
       </c>
       <c r="B176" s="27" t="inlineStr">
@@ -13187,17 +13191,17 @@
       </c>
       <c r="C176" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D176" s="27" t="inlineStr">
         <is>
-          <t>Service technician hiring</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E176" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F176" s="27" t="inlineStr">
@@ -13207,11 +13211,11 @@
       </c>
       <c r="G176" s="27" t="inlineStr">
         <is>
-          <t>Annual EBITDA impact</t>
+          <t>Forecast opex</t>
         </is>
       </c>
       <c r="H176" s="44" t="n">
-        <v>620000</v>
+        <v>1060000</v>
       </c>
       <c r="I176" s="27" t="inlineStr"/>
       <c r="J176" s="27" t="inlineStr">
@@ -13234,7 +13238,7 @@
     <row r="177">
       <c r="A177" s="36" t="inlineStr">
         <is>
-          <t>RPT-00380</t>
+          <t>RPT-00366</t>
         </is>
       </c>
       <c r="B177" s="27" t="inlineStr">
@@ -13244,17 +13248,17 @@
       </c>
       <c r="C177" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board operating outlook</t>
         </is>
       </c>
       <c r="D177" s="27" t="inlineStr">
         <is>
-          <t>Service technician hiring</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E177" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F177" s="27" t="inlineStr">
@@ -13264,16 +13268,16 @@
       </c>
       <c r="G177" s="27" t="inlineStr">
         <is>
-          <t>Realization probability</t>
+          <t>Plan opex</t>
         </is>
       </c>
       <c r="H177" s="44" t="n">
-        <v>0.7</v>
+        <v>1120000</v>
       </c>
       <c r="I177" s="27" t="inlineStr"/>
       <c r="J177" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K177" s="27" t="inlineStr">
@@ -13291,7 +13295,7 @@
     <row r="178">
       <c r="A178" s="36" t="inlineStr">
         <is>
-          <t>RPT-00381</t>
+          <t>RPT-00367</t>
         </is>
       </c>
       <c r="B178" s="27" t="inlineStr">
@@ -13301,17 +13305,17 @@
       </c>
       <c r="C178" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board risk outlook</t>
         </is>
       </c>
       <c r="D178" s="27" t="inlineStr">
         <is>
-          <t>Service technician hiring</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E178" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="F178" s="27" t="inlineStr">
@@ -13321,18 +13325,16 @@
       </c>
       <c r="G178" s="27" t="inlineStr">
         <is>
-          <t>Management status</t>
-        </is>
-      </c>
-      <c r="H178" s="44" t="inlineStr"/>
-      <c r="I178" s="27" t="inlineStr">
-        <is>
-          <t>Approve with gate</t>
-        </is>
-      </c>
+          <t>Covenant EBITDA</t>
+        </is>
+      </c>
+      <c r="H178" s="44" t="n">
+        <v>5520000</v>
+      </c>
+      <c r="I178" s="27" t="inlineStr"/>
       <c r="J178" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K178" s="27" t="inlineStr">
@@ -13350,7 +13352,7 @@
     <row r="179">
       <c r="A179" s="36" t="inlineStr">
         <is>
-          <t>RPT-00382</t>
+          <t>RPT-00368</t>
         </is>
       </c>
       <c r="B179" s="27" t="inlineStr">
@@ -13360,17 +13362,17 @@
       </c>
       <c r="C179" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board risk outlook</t>
         </is>
       </c>
       <c r="D179" s="27" t="inlineStr">
         <is>
-          <t>Boise branch</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E179" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="F179" s="27" t="inlineStr">
@@ -13380,16 +13382,16 @@
       </c>
       <c r="G179" s="27" t="inlineStr">
         <is>
-          <t>Annual EBITDA impact</t>
+          <t>Ending cash before financing</t>
         </is>
       </c>
       <c r="H179" s="44" t="n">
-        <v>450000</v>
+        <v>3850</v>
       </c>
       <c r="I179" s="27" t="inlineStr"/>
       <c r="J179" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K179" s="27" t="inlineStr">
@@ -13407,7 +13409,7 @@
     <row r="180">
       <c r="A180" s="36" t="inlineStr">
         <is>
-          <t>RPT-00383</t>
+          <t>RPT-00369</t>
         </is>
       </c>
       <c r="B180" s="27" t="inlineStr">
@@ -13417,17 +13419,17 @@
       </c>
       <c r="C180" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board risk outlook</t>
         </is>
       </c>
       <c r="D180" s="27" t="inlineStr">
         <is>
-          <t>Boise branch</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E180" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="F180" s="27" t="inlineStr">
@@ -13437,16 +13439,16 @@
       </c>
       <c r="G180" s="27" t="inlineStr">
         <is>
-          <t>Realization probability</t>
+          <t>Revolver balance</t>
         </is>
       </c>
       <c r="H180" s="44" t="n">
-        <v>0.45</v>
+        <v>2900000</v>
       </c>
       <c r="I180" s="27" t="inlineStr"/>
       <c r="J180" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K180" s="27" t="inlineStr">
@@ -13464,7 +13466,7 @@
     <row r="181">
       <c r="A181" s="36" t="inlineStr">
         <is>
-          <t>RPT-00384</t>
+          <t>RPT-00370</t>
         </is>
       </c>
       <c r="B181" s="27" t="inlineStr">
@@ -13474,17 +13476,17 @@
       </c>
       <c r="C181" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board risk outlook</t>
         </is>
       </c>
       <c r="D181" s="27" t="inlineStr">
         <is>
-          <t>Boise branch</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E181" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Downside</t>
         </is>
       </c>
       <c r="F181" s="27" t="inlineStr">
@@ -13494,18 +13496,16 @@
       </c>
       <c r="G181" s="27" t="inlineStr">
         <is>
-          <t>Management status</t>
-        </is>
-      </c>
-      <c r="H181" s="44" t="inlineStr"/>
-      <c r="I181" s="27" t="inlineStr">
-        <is>
-          <t>Defer</t>
-        </is>
-      </c>
+          <t>Covenant EBITDA</t>
+        </is>
+      </c>
+      <c r="H181" s="44" t="n">
+        <v>3780000</v>
+      </c>
+      <c r="I181" s="27" t="inlineStr"/>
       <c r="J181" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K181" s="27" t="inlineStr">
@@ -13523,7 +13523,7 @@
     <row r="182">
       <c r="A182" s="36" t="inlineStr">
         <is>
-          <t>RPT-00385</t>
+          <t>RPT-00371</t>
         </is>
       </c>
       <c r="B182" s="27" t="inlineStr">
@@ -13533,17 +13533,17 @@
       </c>
       <c r="C182" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board risk outlook</t>
         </is>
       </c>
       <c r="D182" s="27" t="inlineStr">
         <is>
-          <t>Pioneer acquisition</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E182" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Downside</t>
         </is>
       </c>
       <c r="F182" s="27" t="inlineStr">
@@ -13553,11 +13553,11 @@
       </c>
       <c r="G182" s="27" t="inlineStr">
         <is>
-          <t>Annual EBITDA impact</t>
+          <t>Ending cash before financing</t>
         </is>
       </c>
       <c r="H182" s="44" t="n">
-        <v>1250000</v>
+        <v>1950000</v>
       </c>
       <c r="I182" s="27" t="inlineStr"/>
       <c r="J182" s="27" t="inlineStr">
@@ -13580,7 +13580,7 @@
     <row r="183">
       <c r="A183" s="36" t="inlineStr">
         <is>
-          <t>RPT-00386</t>
+          <t>RPT-00372</t>
         </is>
       </c>
       <c r="B183" s="27" t="inlineStr">
@@ -13590,17 +13590,17 @@
       </c>
       <c r="C183" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board risk outlook</t>
         </is>
       </c>
       <c r="D183" s="27" t="inlineStr">
         <is>
-          <t>Pioneer acquisition</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E183" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Downside</t>
         </is>
       </c>
       <c r="F183" s="27" t="inlineStr">
@@ -13610,16 +13610,16 @@
       </c>
       <c r="G183" s="27" t="inlineStr">
         <is>
-          <t>Realization probability</t>
+          <t>Revolver balance</t>
         </is>
       </c>
       <c r="H183" s="44" t="n">
-        <v>0.6</v>
+        <v>4600</v>
       </c>
       <c r="I183" s="27" t="inlineStr"/>
       <c r="J183" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K183" s="27" t="inlineStr">
@@ -13637,7 +13637,7 @@
     <row r="184">
       <c r="A184" s="36" t="inlineStr">
         <is>
-          <t>RPT-00387</t>
+          <t>RPT-00373</t>
         </is>
       </c>
       <c r="B184" s="27" t="inlineStr">
@@ -13647,17 +13647,17 @@
       </c>
       <c r="C184" s="27" t="inlineStr">
         <is>
-          <t>Board strategic priorities</t>
+          <t>Board risk outlook</t>
         </is>
       </c>
       <c r="D184" s="27" t="inlineStr">
         <is>
-          <t>Pioneer acquisition</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E184" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>Severe</t>
         </is>
       </c>
       <c r="F184" s="27" t="inlineStr">
@@ -13667,18 +13667,16 @@
       </c>
       <c r="G184" s="27" t="inlineStr">
         <is>
-          <t>Management status</t>
-        </is>
-      </c>
-      <c r="H184" s="44" t="inlineStr"/>
-      <c r="I184" s="27" t="inlineStr">
-        <is>
-          <t>Conditional</t>
-        </is>
-      </c>
+          <t>Covenant EBITDA</t>
+        </is>
+      </c>
+      <c r="H184" s="44" t="n">
+        <v>2650000</v>
+      </c>
+      <c r="I184" s="27" t="inlineStr"/>
       <c r="J184" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K184" s="27" t="inlineStr">
@@ -13696,7 +13694,7 @@
     <row r="185">
       <c r="A185" s="36" t="inlineStr">
         <is>
-          <t>RPT-00388</t>
+          <t>RPT-00374</t>
         </is>
       </c>
       <c r="B185" s="27" t="inlineStr">
@@ -13706,7 +13704,7 @@
       </c>
       <c r="C185" s="27" t="inlineStr">
         <is>
-          <t>Board presentation controls</t>
+          <t>Board risk outlook</t>
         </is>
       </c>
       <c r="D185" s="27" t="inlineStr">
@@ -13716,7 +13714,7 @@
       </c>
       <c r="E185" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>Severe</t>
         </is>
       </c>
       <c r="F185" s="27" t="inlineStr">
@@ -13726,16 +13724,16 @@
       </c>
       <c r="G185" s="27" t="inlineStr">
         <is>
-          <t>Minimum cash</t>
+          <t>Ending cash before financing</t>
         </is>
       </c>
       <c r="H185" s="44" t="n">
-        <v>2250</v>
+        <v>820000</v>
       </c>
       <c r="I185" s="27" t="inlineStr"/>
       <c r="J185" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K185" s="27" t="inlineStr">
@@ -13753,7 +13751,7 @@
     <row r="186">
       <c r="A186" s="36" t="inlineStr">
         <is>
-          <t>RPT-00389</t>
+          <t>RPT-00375</t>
         </is>
       </c>
       <c r="B186" s="27" t="inlineStr">
@@ -13763,7 +13761,7 @@
       </c>
       <c r="C186" s="27" t="inlineStr">
         <is>
-          <t>Board presentation controls</t>
+          <t>Board risk outlook</t>
         </is>
       </c>
       <c r="D186" s="27" t="inlineStr">
@@ -13773,7 +13771,7 @@
       </c>
       <c r="E186" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>Severe</t>
         </is>
       </c>
       <c r="F186" s="27" t="inlineStr">
@@ -13783,11 +13781,11 @@
       </c>
       <c r="G186" s="27" t="inlineStr">
         <is>
-          <t>Revolver commitment</t>
+          <t>Revolver balance</t>
         </is>
       </c>
       <c r="H186" s="44" t="n">
-        <v>8000000</v>
+        <v>6900000</v>
       </c>
       <c r="I186" s="27" t="inlineStr"/>
       <c r="J186" s="27" t="inlineStr">
@@ -13810,7 +13808,7 @@
     <row r="187">
       <c r="A187" s="36" t="inlineStr">
         <is>
-          <t>RPT-00390</t>
+          <t>RPT-00376</t>
         </is>
       </c>
       <c r="B187" s="27" t="inlineStr">
@@ -13820,17 +13818,17 @@
       </c>
       <c r="C187" s="27" t="inlineStr">
         <is>
-          <t>Board presentation controls</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D187" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Procurement program</t>
         </is>
       </c>
       <c r="E187" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="F187" s="27" t="inlineStr">
@@ -13840,16 +13838,16 @@
       </c>
       <c r="G187" s="27" t="inlineStr">
         <is>
-          <t>Maximum leverage</t>
+          <t>Annual EBITDA impact</t>
         </is>
       </c>
       <c r="H187" s="44" t="n">
-        <v>2.5</v>
+        <v>780</v>
       </c>
       <c r="I187" s="27" t="inlineStr"/>
       <c r="J187" s="27" t="inlineStr">
         <is>
-          <t>multiple</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K187" s="27" t="inlineStr">
@@ -13867,7 +13865,7 @@
     <row r="188">
       <c r="A188" s="36" t="inlineStr">
         <is>
-          <t>RPT-00391</t>
+          <t>RPT-00377</t>
         </is>
       </c>
       <c r="B188" s="27" t="inlineStr">
@@ -13877,17 +13875,17 @@
       </c>
       <c r="C188" s="27" t="inlineStr">
         <is>
-          <t>Board presentation controls</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D188" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Procurement program</t>
         </is>
       </c>
       <c r="E188" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="F188" s="27" t="inlineStr">
@@ -13897,16 +13895,16 @@
       </c>
       <c r="G188" s="27" t="inlineStr">
         <is>
-          <t>Funded debt before revolver</t>
+          <t>Realization probability</t>
         </is>
       </c>
       <c r="H188" s="44" t="n">
-        <v>7400000</v>
+        <v>0.8</v>
       </c>
       <c r="I188" s="27" t="inlineStr"/>
       <c r="J188" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K188" s="27" t="inlineStr">
@@ -13924,7 +13922,7 @@
     <row r="189">
       <c r="A189" s="36" t="inlineStr">
         <is>
-          <t>RPT-00392</t>
+          <t>RPT-00378</t>
         </is>
       </c>
       <c r="B189" s="27" t="inlineStr">
@@ -13934,17 +13932,17 @@
       </c>
       <c r="C189" s="27" t="inlineStr">
         <is>
-          <t>Board presentation controls</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D189" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Procurement program</t>
         </is>
       </c>
       <c r="E189" s="27" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="F189" s="27" t="inlineStr">
@@ -13954,16 +13952,18 @@
       </c>
       <c r="G189" s="27" t="inlineStr">
         <is>
-          <t>Board-approved AOP revenue</t>
-        </is>
-      </c>
-      <c r="H189" s="44" t="n">
-        <v>47920</v>
-      </c>
-      <c r="I189" s="27" t="inlineStr"/>
+          <t>Management status</t>
+        </is>
+      </c>
+      <c r="H189" s="44" t="inlineStr"/>
+      <c r="I189" s="27" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
       <c r="J189" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K189" s="27" t="inlineStr">
@@ -13981,7 +13981,7 @@
     <row r="190">
       <c r="A190" s="36" t="inlineStr">
         <is>
-          <t>RPT-00409</t>
+          <t>RPT-00379</t>
         </is>
       </c>
       <c r="B190" s="27" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="C190" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D190" s="27" t="inlineStr">
         <is>
-          <t>Procurement program</t>
+          <t>Service technician hiring</t>
         </is>
       </c>
       <c r="E190" s="27" t="inlineStr">
@@ -14011,11 +14011,11 @@
       </c>
       <c r="G190" s="27" t="inlineStr">
         <is>
-          <t>Cash investment</t>
+          <t>Annual EBITDA impact</t>
         </is>
       </c>
       <c r="H190" s="44" t="n">
-        <v>420000</v>
+        <v>620000</v>
       </c>
       <c r="I190" s="27" t="inlineStr"/>
       <c r="J190" s="27" t="inlineStr">
@@ -14038,7 +14038,7 @@
     <row r="191">
       <c r="A191" s="36" t="inlineStr">
         <is>
-          <t>RPT-00410</t>
+          <t>RPT-00380</t>
         </is>
       </c>
       <c r="B191" s="27" t="inlineStr">
@@ -14048,12 +14048,12 @@
       </c>
       <c r="C191" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D191" s="27" t="inlineStr">
         <is>
-          <t>Procurement program</t>
+          <t>Service technician hiring</t>
         </is>
       </c>
       <c r="E191" s="27" t="inlineStr">
@@ -14068,14 +14068,16 @@
       </c>
       <c r="G191" s="27" t="inlineStr">
         <is>
-          <t>Dependency</t>
-        </is>
-      </c>
-      <c r="H191" s="44" t="inlineStr"/>
+          <t>Realization probability</t>
+        </is>
+      </c>
+      <c r="H191" s="44" t="n">
+        <v>0.7</v>
+      </c>
       <c r="I191" s="27" t="inlineStr"/>
       <c r="J191" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K191" s="27" t="inlineStr">
@@ -14093,7 +14095,7 @@
     <row r="192">
       <c r="A192" s="36" t="inlineStr">
         <is>
-          <t>RPT-00411</t>
+          <t>RPT-00381</t>
         </is>
       </c>
       <c r="B192" s="27" t="inlineStr">
@@ -14103,12 +14105,12 @@
       </c>
       <c r="C192" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D192" s="27" t="inlineStr">
         <is>
-          <t>Procurement program</t>
+          <t>Service technician hiring</t>
         </is>
       </c>
       <c r="E192" s="27" t="inlineStr">
@@ -14123,16 +14125,18 @@
       </c>
       <c r="G192" s="27" t="inlineStr">
         <is>
-          <t>Severe benefit factor</t>
-        </is>
-      </c>
-      <c r="H192" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I192" s="27" t="inlineStr"/>
+          <t>Management status</t>
+        </is>
+      </c>
+      <c r="H192" s="44" t="inlineStr"/>
+      <c r="I192" s="27" t="inlineStr">
+        <is>
+          <t>Approve with gate</t>
+        </is>
+      </c>
       <c r="J192" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K192" s="27" t="inlineStr">
@@ -14150,7 +14154,7 @@
     <row r="193">
       <c r="A193" s="36" t="inlineStr">
         <is>
-          <t>RPT-00412</t>
+          <t>RPT-00382</t>
         </is>
       </c>
       <c r="B193" s="27" t="inlineStr">
@@ -14160,12 +14164,12 @@
       </c>
       <c r="C193" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D193" s="27" t="inlineStr">
         <is>
-          <t>Service technician hiring</t>
+          <t>Boise branch</t>
         </is>
       </c>
       <c r="E193" s="27" t="inlineStr">
@@ -14180,16 +14184,16 @@
       </c>
       <c r="G193" s="27" t="inlineStr">
         <is>
-          <t>Cash investment</t>
+          <t>Annual EBITDA impact</t>
         </is>
       </c>
       <c r="H193" s="44" t="n">
-        <v>610</v>
+        <v>450000</v>
       </c>
       <c r="I193" s="27" t="inlineStr"/>
       <c r="J193" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K193" s="27" t="inlineStr">
@@ -14207,7 +14211,7 @@
     <row r="194">
       <c r="A194" s="36" t="inlineStr">
         <is>
-          <t>RPT-00413</t>
+          <t>RPT-00383</t>
         </is>
       </c>
       <c r="B194" s="27" t="inlineStr">
@@ -14217,12 +14221,12 @@
       </c>
       <c r="C194" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D194" s="27" t="inlineStr">
         <is>
-          <t>Service technician hiring</t>
+          <t>Boise branch</t>
         </is>
       </c>
       <c r="E194" s="27" t="inlineStr">
@@ -14237,18 +14241,16 @@
       </c>
       <c r="G194" s="27" t="inlineStr">
         <is>
-          <t>Dependency</t>
-        </is>
-      </c>
-      <c r="H194" s="44" t="inlineStr"/>
-      <c r="I194" s="27" t="inlineStr">
-        <is>
-          <t>Procurement program</t>
-        </is>
-      </c>
+          <t>Realization probability</t>
+        </is>
+      </c>
+      <c r="H194" s="44" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I194" s="27" t="inlineStr"/>
       <c r="J194" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K194" s="27" t="inlineStr">
@@ -14266,7 +14268,7 @@
     <row r="195">
       <c r="A195" s="36" t="inlineStr">
         <is>
-          <t>RPT-00414</t>
+          <t>RPT-00384</t>
         </is>
       </c>
       <c r="B195" s="27" t="inlineStr">
@@ -14276,12 +14278,12 @@
       </c>
       <c r="C195" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D195" s="27" t="inlineStr">
         <is>
-          <t>Service technician hiring</t>
+          <t>Boise branch</t>
         </is>
       </c>
       <c r="E195" s="27" t="inlineStr">
@@ -14296,16 +14298,18 @@
       </c>
       <c r="G195" s="27" t="inlineStr">
         <is>
-          <t>Severe benefit factor</t>
-        </is>
-      </c>
-      <c r="H195" s="44" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I195" s="27" t="inlineStr"/>
+          <t>Management status</t>
+        </is>
+      </c>
+      <c r="H195" s="44" t="inlineStr"/>
+      <c r="I195" s="27" t="inlineStr">
+        <is>
+          <t>Defer</t>
+        </is>
+      </c>
       <c r="J195" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K195" s="27" t="inlineStr">
@@ -14323,7 +14327,7 @@
     <row r="196">
       <c r="A196" s="36" t="inlineStr">
         <is>
-          <t>RPT-00415</t>
+          <t>RPT-00385</t>
         </is>
       </c>
       <c r="B196" s="27" t="inlineStr">
@@ -14333,12 +14337,12 @@
       </c>
       <c r="C196" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D196" s="27" t="inlineStr">
         <is>
-          <t>Boise branch</t>
+          <t>Pioneer acquisition</t>
         </is>
       </c>
       <c r="E196" s="27" t="inlineStr">
@@ -14353,11 +14357,11 @@
       </c>
       <c r="G196" s="27" t="inlineStr">
         <is>
-          <t>Cash investment</t>
+          <t>Annual EBITDA impact</t>
         </is>
       </c>
       <c r="H196" s="44" t="n">
-        <v>880000</v>
+        <v>1250000</v>
       </c>
       <c r="I196" s="27" t="inlineStr"/>
       <c r="J196" s="27" t="inlineStr">
@@ -14380,7 +14384,7 @@
     <row r="197">
       <c r="A197" s="36" t="inlineStr">
         <is>
-          <t>RPT-00416</t>
+          <t>RPT-00386</t>
         </is>
       </c>
       <c r="B197" s="27" t="inlineStr">
@@ -14390,12 +14394,12 @@
       </c>
       <c r="C197" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D197" s="27" t="inlineStr">
         <is>
-          <t>Boise branch</t>
+          <t>Pioneer acquisition</t>
         </is>
       </c>
       <c r="E197" s="27" t="inlineStr">
@@ -14410,18 +14414,16 @@
       </c>
       <c r="G197" s="27" t="inlineStr">
         <is>
-          <t>Dependency</t>
-        </is>
-      </c>
-      <c r="H197" s="44" t="inlineStr"/>
-      <c r="I197" s="27" t="inlineStr">
-        <is>
-          <t>Service technician hiring</t>
-        </is>
-      </c>
+          <t>Realization probability</t>
+        </is>
+      </c>
+      <c r="H197" s="44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I197" s="27" t="inlineStr"/>
       <c r="J197" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K197" s="27" t="inlineStr">
@@ -14439,7 +14441,7 @@
     <row r="198">
       <c r="A198" s="36" t="inlineStr">
         <is>
-          <t>RPT-00417</t>
+          <t>RPT-00387</t>
         </is>
       </c>
       <c r="B198" s="27" t="inlineStr">
@@ -14449,12 +14451,12 @@
       </c>
       <c r="C198" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board strategic priorities</t>
         </is>
       </c>
       <c r="D198" s="27" t="inlineStr">
         <is>
-          <t>Boise branch</t>
+          <t>Pioneer acquisition</t>
         </is>
       </c>
       <c r="E198" s="27" t="inlineStr">
@@ -14469,16 +14471,18 @@
       </c>
       <c r="G198" s="27" t="inlineStr">
         <is>
-          <t>Severe benefit factor</t>
-        </is>
-      </c>
-      <c r="H198" s="44" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I198" s="27" t="inlineStr"/>
+          <t>Management status</t>
+        </is>
+      </c>
+      <c r="H198" s="44" t="inlineStr"/>
+      <c r="I198" s="27" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
       <c r="J198" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K198" s="27" t="inlineStr">
@@ -14496,7 +14500,7 @@
     <row r="199">
       <c r="A199" s="36" t="inlineStr">
         <is>
-          <t>RPT-00418</t>
+          <t>RPT-00388</t>
         </is>
       </c>
       <c r="B199" s="27" t="inlineStr">
@@ -14506,17 +14510,17 @@
       </c>
       <c r="C199" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board presentation controls</t>
         </is>
       </c>
       <c r="D199" s="27" t="inlineStr">
         <is>
-          <t>Pioneer acquisition</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E199" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F199" s="27" t="inlineStr">
@@ -14526,16 +14530,16 @@
       </c>
       <c r="G199" s="27" t="inlineStr">
         <is>
-          <t>Cash investment</t>
+          <t>Minimum cash</t>
         </is>
       </c>
       <c r="H199" s="44" t="n">
-        <v>1150000</v>
+        <v>2250</v>
       </c>
       <c r="I199" s="27" t="inlineStr"/>
       <c r="J199" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K199" s="27" t="inlineStr">
@@ -14553,7 +14557,7 @@
     <row r="200">
       <c r="A200" s="36" t="inlineStr">
         <is>
-          <t>RPT-00419</t>
+          <t>RPT-00389</t>
         </is>
       </c>
       <c r="B200" s="27" t="inlineStr">
@@ -14563,17 +14567,17 @@
       </c>
       <c r="C200" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board presentation controls</t>
         </is>
       </c>
       <c r="D200" s="27" t="inlineStr">
         <is>
-          <t>Pioneer acquisition</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E200" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F200" s="27" t="inlineStr">
@@ -14583,18 +14587,16 @@
       </c>
       <c r="G200" s="27" t="inlineStr">
         <is>
-          <t>Dependency</t>
-        </is>
-      </c>
-      <c r="H200" s="44" t="inlineStr"/>
-      <c r="I200" s="27" t="inlineStr">
-        <is>
-          <t>Procurement program</t>
-        </is>
-      </c>
+          <t>Revolver commitment</t>
+        </is>
+      </c>
+      <c r="H200" s="44" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I200" s="27" t="inlineStr"/>
       <c r="J200" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K200" s="27" t="inlineStr">
@@ -14612,7 +14614,7 @@
     <row r="201">
       <c r="A201" s="36" t="inlineStr">
         <is>
-          <t>RPT-00420</t>
+          <t>RPT-00390</t>
         </is>
       </c>
       <c r="B201" s="27" t="inlineStr">
@@ -14622,17 +14624,17 @@
       </c>
       <c r="C201" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio</t>
+          <t>Board presentation controls</t>
         </is>
       </c>
       <c r="D201" s="27" t="inlineStr">
         <is>
-          <t>Pioneer acquisition</t>
+          <t>Alder Ridge</t>
         </is>
       </c>
       <c r="E201" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F201" s="27" t="inlineStr">
@@ -14642,16 +14644,16 @@
       </c>
       <c r="G201" s="27" t="inlineStr">
         <is>
-          <t>Severe benefit factor</t>
+          <t>Maximum leverage</t>
         </is>
       </c>
       <c r="H201" s="44" t="n">
-        <v>0.45</v>
+        <v>2.5</v>
       </c>
       <c r="I201" s="27" t="inlineStr"/>
       <c r="J201" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="K201" s="27" t="inlineStr">
@@ -14669,7 +14671,7 @@
     <row r="202">
       <c r="A202" s="36" t="inlineStr">
         <is>
-          <t>RPT-00421</t>
+          <t>RPT-00391</t>
         </is>
       </c>
       <c r="B202" s="27" t="inlineStr">
@@ -14679,7 +14681,7 @@
       </c>
       <c r="C202" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio policy</t>
+          <t>Board presentation controls</t>
         </is>
       </c>
       <c r="D202" s="27" t="inlineStr">
@@ -14689,7 +14691,7 @@
       </c>
       <c r="E202" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F202" s="27" t="inlineStr">
@@ -14699,11 +14701,11 @@
       </c>
       <c r="G202" s="27" t="inlineStr">
         <is>
-          <t>Decision cash budget</t>
+          <t>Funded debt before revolver</t>
         </is>
       </c>
       <c r="H202" s="44" t="n">
-        <v>1550000</v>
+        <v>7400000</v>
       </c>
       <c r="I202" s="27" t="inlineStr"/>
       <c r="J202" s="27" t="inlineStr">
@@ -14726,7 +14728,7 @@
     <row r="203">
       <c r="A203" s="36" t="inlineStr">
         <is>
-          <t>RPT-00422</t>
+          <t>RPT-00392</t>
         </is>
       </c>
       <c r="B203" s="27" t="inlineStr">
@@ -14736,7 +14738,7 @@
       </c>
       <c r="C203" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio policy</t>
+          <t>Board presentation controls</t>
         </is>
       </c>
       <c r="D203" s="27" t="inlineStr">
@@ -14746,7 +14748,7 @@
       </c>
       <c r="E203" s="27" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="F203" s="27" t="inlineStr">
@@ -14756,16 +14758,16 @@
       </c>
       <c r="G203" s="27" t="inlineStr">
         <is>
-          <t>Maximum active initiatives</t>
+          <t>Board-approved AOP revenue</t>
         </is>
       </c>
       <c r="H203" s="44" t="n">
-        <v>2</v>
+        <v>47920</v>
       </c>
       <c r="I203" s="27" t="inlineStr"/>
       <c r="J203" s="27" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K203" s="27" t="inlineStr">
@@ -14783,7 +14785,7 @@
     <row r="204">
       <c r="A204" s="36" t="inlineStr">
         <is>
-          <t>RPT-00423</t>
+          <t>RPT-00409</t>
         </is>
       </c>
       <c r="B204" s="27" t="inlineStr">
@@ -14793,12 +14795,12 @@
       </c>
       <c r="C204" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio policy</t>
+          <t>Board decision portfolio</t>
         </is>
       </c>
       <c r="D204" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Procurement program</t>
         </is>
       </c>
       <c r="E204" s="27" t="inlineStr">
@@ -14813,16 +14815,16 @@
       </c>
       <c r="G204" s="27" t="inlineStr">
         <is>
-          <t>Severe EBITDA cash conversion</t>
+          <t>Cash investment</t>
         </is>
       </c>
       <c r="H204" s="44" t="n">
-        <v>0.7</v>
+        <v>420000</v>
       </c>
       <c r="I204" s="27" t="inlineStr"/>
       <c r="J204" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K204" s="27" t="inlineStr">
@@ -14840,7 +14842,7 @@
     <row r="205">
       <c r="A205" s="36" t="inlineStr">
         <is>
-          <t>RPT-00424</t>
+          <t>RPT-00410</t>
         </is>
       </c>
       <c r="B205" s="27" t="inlineStr">
@@ -14850,12 +14852,12 @@
       </c>
       <c r="C205" s="27" t="inlineStr">
         <is>
-          <t>Board decision portfolio policy</t>
+          <t>Board decision portfolio</t>
         </is>
       </c>
       <c r="D205" s="27" t="inlineStr">
         <is>
-          <t>Alder Ridge</t>
+          <t>Procurement program</t>
         </is>
       </c>
       <c r="E205" s="27" t="inlineStr">
@@ -14870,15 +14872,11 @@
       </c>
       <c r="G205" s="27" t="inlineStr">
         <is>
-          <t>Eligible statuses</t>
+          <t>Dependency</t>
         </is>
       </c>
       <c r="H205" s="44" t="inlineStr"/>
-      <c r="I205" s="27" t="inlineStr">
-        <is>
-          <t>Approve; Approve with gate; Conditional</t>
-        </is>
-      </c>
+      <c r="I205" s="27" t="inlineStr"/>
       <c r="J205" s="27" t="inlineStr">
         <is>
           <t>classification</t>
@@ -14899,64 +14897,870 @@
     <row r="206">
       <c r="A206" s="36" t="inlineStr">
         <is>
+          <t>RPT-00411</t>
+        </is>
+      </c>
+      <c r="B206" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C206" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio</t>
+        </is>
+      </c>
+      <c r="D206" s="27" t="inlineStr">
+        <is>
+          <t>Procurement program</t>
+        </is>
+      </c>
+      <c r="E206" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F206" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G206" s="27" t="inlineStr">
+        <is>
+          <t>Severe benefit factor</t>
+        </is>
+      </c>
+      <c r="H206" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" s="27" t="inlineStr"/>
+      <c r="J206" s="27" t="inlineStr">
+        <is>
+          <t>decimal ratio</t>
+        </is>
+      </c>
+      <c r="K206" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L206" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M206" s="27" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00412</t>
+        </is>
+      </c>
+      <c r="B207" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C207" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio</t>
+        </is>
+      </c>
+      <c r="D207" s="27" t="inlineStr">
+        <is>
+          <t>Service technician hiring</t>
+        </is>
+      </c>
+      <c r="E207" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F207" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G207" s="27" t="inlineStr">
+        <is>
+          <t>Cash investment</t>
+        </is>
+      </c>
+      <c r="H207" s="44" t="n">
+        <v>610</v>
+      </c>
+      <c r="I207" s="27" t="inlineStr"/>
+      <c r="J207" s="27" t="inlineStr">
+        <is>
+          <t>USD thousands</t>
+        </is>
+      </c>
+      <c r="K207" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L207" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M207" s="27" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00413</t>
+        </is>
+      </c>
+      <c r="B208" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C208" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio</t>
+        </is>
+      </c>
+      <c r="D208" s="27" t="inlineStr">
+        <is>
+          <t>Service technician hiring</t>
+        </is>
+      </c>
+      <c r="E208" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F208" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G208" s="27" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="H208" s="44" t="inlineStr"/>
+      <c r="I208" s="27" t="inlineStr">
+        <is>
+          <t>Procurement program</t>
+        </is>
+      </c>
+      <c r="J208" s="27" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="K208" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L208" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M208" s="27" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00414</t>
+        </is>
+      </c>
+      <c r="B209" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C209" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio</t>
+        </is>
+      </c>
+      <c r="D209" s="27" t="inlineStr">
+        <is>
+          <t>Service technician hiring</t>
+        </is>
+      </c>
+      <c r="E209" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F209" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G209" s="27" t="inlineStr">
+        <is>
+          <t>Severe benefit factor</t>
+        </is>
+      </c>
+      <c r="H209" s="44" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I209" s="27" t="inlineStr"/>
+      <c r="J209" s="27" t="inlineStr">
+        <is>
+          <t>decimal ratio</t>
+        </is>
+      </c>
+      <c r="K209" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L209" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M209" s="27" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00415</t>
+        </is>
+      </c>
+      <c r="B210" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C210" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio</t>
+        </is>
+      </c>
+      <c r="D210" s="27" t="inlineStr">
+        <is>
+          <t>Boise branch</t>
+        </is>
+      </c>
+      <c r="E210" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F210" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G210" s="27" t="inlineStr">
+        <is>
+          <t>Cash investment</t>
+        </is>
+      </c>
+      <c r="H210" s="44" t="n">
+        <v>880000</v>
+      </c>
+      <c r="I210" s="27" t="inlineStr"/>
+      <c r="J210" s="27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K210" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L210" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M210" s="27" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00416</t>
+        </is>
+      </c>
+      <c r="B211" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C211" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio</t>
+        </is>
+      </c>
+      <c r="D211" s="27" t="inlineStr">
+        <is>
+          <t>Boise branch</t>
+        </is>
+      </c>
+      <c r="E211" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F211" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G211" s="27" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="H211" s="44" t="inlineStr"/>
+      <c r="I211" s="27" t="inlineStr">
+        <is>
+          <t>Service technician hiring</t>
+        </is>
+      </c>
+      <c r="J211" s="27" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="K211" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L211" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M211" s="27" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00417</t>
+        </is>
+      </c>
+      <c r="B212" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C212" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio</t>
+        </is>
+      </c>
+      <c r="D212" s="27" t="inlineStr">
+        <is>
+          <t>Boise branch</t>
+        </is>
+      </c>
+      <c r="E212" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F212" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G212" s="27" t="inlineStr">
+        <is>
+          <t>Severe benefit factor</t>
+        </is>
+      </c>
+      <c r="H212" s="44" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I212" s="27" t="inlineStr"/>
+      <c r="J212" s="27" t="inlineStr">
+        <is>
+          <t>decimal ratio</t>
+        </is>
+      </c>
+      <c r="K212" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L212" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M212" s="27" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00418</t>
+        </is>
+      </c>
+      <c r="B213" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C213" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio</t>
+        </is>
+      </c>
+      <c r="D213" s="27" t="inlineStr">
+        <is>
+          <t>Pioneer acquisition</t>
+        </is>
+      </c>
+      <c r="E213" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F213" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G213" s="27" t="inlineStr">
+        <is>
+          <t>Cash investment</t>
+        </is>
+      </c>
+      <c r="H213" s="44" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="I213" s="27" t="inlineStr"/>
+      <c r="J213" s="27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K213" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L213" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M213" s="27" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00419</t>
+        </is>
+      </c>
+      <c r="B214" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C214" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio</t>
+        </is>
+      </c>
+      <c r="D214" s="27" t="inlineStr">
+        <is>
+          <t>Pioneer acquisition</t>
+        </is>
+      </c>
+      <c r="E214" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F214" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G214" s="27" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="H214" s="44" t="inlineStr"/>
+      <c r="I214" s="27" t="inlineStr">
+        <is>
+          <t>Procurement program</t>
+        </is>
+      </c>
+      <c r="J214" s="27" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="K214" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L214" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M214" s="27" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00420</t>
+        </is>
+      </c>
+      <c r="B215" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C215" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio</t>
+        </is>
+      </c>
+      <c r="D215" s="27" t="inlineStr">
+        <is>
+          <t>Pioneer acquisition</t>
+        </is>
+      </c>
+      <c r="E215" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F215" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G215" s="27" t="inlineStr">
+        <is>
+          <t>Severe benefit factor</t>
+        </is>
+      </c>
+      <c r="H215" s="44" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I215" s="27" t="inlineStr"/>
+      <c r="J215" s="27" t="inlineStr">
+        <is>
+          <t>decimal ratio</t>
+        </is>
+      </c>
+      <c r="K215" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L215" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M215" s="27" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00421</t>
+        </is>
+      </c>
+      <c r="B216" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C216" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio policy</t>
+        </is>
+      </c>
+      <c r="D216" s="27" t="inlineStr">
+        <is>
+          <t>Alder Ridge</t>
+        </is>
+      </c>
+      <c r="E216" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F216" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G216" s="27" t="inlineStr">
+        <is>
+          <t>Decision cash budget</t>
+        </is>
+      </c>
+      <c r="H216" s="44" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="I216" s="27" t="inlineStr"/>
+      <c r="J216" s="27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K216" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L216" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M216" s="27" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00422</t>
+        </is>
+      </c>
+      <c r="B217" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C217" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio policy</t>
+        </is>
+      </c>
+      <c r="D217" s="27" t="inlineStr">
+        <is>
+          <t>Alder Ridge</t>
+        </is>
+      </c>
+      <c r="E217" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F217" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G217" s="27" t="inlineStr">
+        <is>
+          <t>Maximum active initiatives</t>
+        </is>
+      </c>
+      <c r="H217" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I217" s="27" t="inlineStr"/>
+      <c r="J217" s="27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="K217" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L217" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M217" s="27" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00423</t>
+        </is>
+      </c>
+      <c r="B218" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C218" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio policy</t>
+        </is>
+      </c>
+      <c r="D218" s="27" t="inlineStr">
+        <is>
+          <t>Alder Ridge</t>
+        </is>
+      </c>
+      <c r="E218" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F218" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G218" s="27" t="inlineStr">
+        <is>
+          <t>Severe EBITDA cash conversion</t>
+        </is>
+      </c>
+      <c r="H218" s="44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I218" s="27" t="inlineStr"/>
+      <c r="J218" s="27" t="inlineStr">
+        <is>
+          <t>decimal ratio</t>
+        </is>
+      </c>
+      <c r="K218" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L218" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M218" s="27" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="36" t="inlineStr">
+        <is>
+          <t>RPT-00424</t>
+        </is>
+      </c>
+      <c r="B219" s="27" t="inlineStr">
+        <is>
+          <t>Create the CFO strategic-finance board deck</t>
+        </is>
+      </c>
+      <c r="C219" s="27" t="inlineStr">
+        <is>
+          <t>Board decision portfolio policy</t>
+        </is>
+      </c>
+      <c r="D219" s="27" t="inlineStr">
+        <is>
+          <t>Alder Ridge</t>
+        </is>
+      </c>
+      <c r="E219" s="27" t="inlineStr">
+        <is>
+          <t>FY27</t>
+        </is>
+      </c>
+      <c r="F219" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G219" s="27" t="inlineStr">
+        <is>
+          <t>Eligible statuses</t>
+        </is>
+      </c>
+      <c r="H219" s="44" t="inlineStr"/>
+      <c r="I219" s="27" t="inlineStr">
+        <is>
+          <t>Approve; Approve with gate; Conditional</t>
+        </is>
+      </c>
+      <c r="J219" s="27" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="K219" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L219" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M219" s="27" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="36" t="inlineStr">
+        <is>
           <t>RPT-00425</t>
         </is>
       </c>
-      <c r="B206" s="27" t="inlineStr">
+      <c r="B220" s="27" t="inlineStr">
         <is>
           <t>Create the CFO strategic-finance board deck</t>
         </is>
       </c>
-      <c r="C206" s="27" t="inlineStr">
+      <c r="C220" s="27" t="inlineStr">
         <is>
           <t>Board decision portfolio policy</t>
         </is>
       </c>
-      <c r="D206" s="27" t="inlineStr">
+      <c r="D220" s="27" t="inlineStr">
         <is>
           <t>Alder Ridge</t>
         </is>
       </c>
-      <c r="E206" s="27" t="inlineStr">
+      <c r="E220" s="27" t="inlineStr">
         <is>
           <t>FY27</t>
         </is>
       </c>
-      <c r="F206" s="27" t="inlineStr">
-        <is>
-          <t>Approved case</t>
-        </is>
-      </c>
-      <c r="G206" s="27" t="inlineStr">
+      <c r="F220" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G220" s="27" t="inlineStr">
         <is>
           <t>Inherited Severe guardrail treatment</t>
         </is>
       </c>
-      <c r="H206" s="44" t="inlineStr"/>
-      <c r="I206" s="27" t="inlineStr">
+      <c r="H220" s="44" t="inlineStr"/>
+      <c r="I220" s="27" t="inlineStr">
         <is>
           <t>Diagnostic after portfolio selection because the no-action Severe baseline already breaches cash and leverage; fund toward the cash floor only up to remaining revolver commitment</t>
         </is>
       </c>
-      <c r="J206" s="27" t="inlineStr">
+      <c r="J220" s="27" t="inlineStr">
         <is>
           <t>classification</t>
         </is>
       </c>
-      <c r="K206" s="27" t="inlineStr">
-        <is>
-          <t>Finance operating schedule</t>
-        </is>
-      </c>
-      <c r="L206" s="45" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="M206" s="27" t="inlineStr"/>
+      <c r="K220" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L220" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M220" s="27" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M206"/>
+  <autoFilter ref="A4:M220"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
